--- a/2025/aux/Formulario para Memoria 2025.xlsx
+++ b/2025/aux/Formulario para Memoria 2025.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="236">
   <si>
     <t xml:space="preserve">FORMULARIO PARA LA CONFECCIÓN DE MEMORIAS DE CENTROS Y GRUPOS</t>
   </si>
@@ -107,6 +107,21 @@
     <t xml:space="preserve">Horas semanales</t>
   </si>
   <si>
+    <t xml:space="preserve">C. Manuel Carlevaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramiro M. Irastorza</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matías Fernández</t>
   </si>
   <si>
@@ -122,16 +137,7 @@
     <t xml:space="preserve">C</t>
   </si>
   <si>
-    <t xml:space="preserve">III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple</t>
-  </si>
-  <si>
     <t xml:space="preserve">Martín Sánchez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
   </si>
   <si>
     <t xml:space="preserve">5.</t>
@@ -304,16 +310,8 @@
 se desarrolló un modelo simplificado de torso, basado en geometrías porcinas, que mostró una influencia moderada del tamaño corporal en el efecto del parche dispersivo, siendo más relevante en individuos pequeños. Por otro lado, experimentalmente, se observó que la radiofrecuencia en tejido desecado genera coagulación hasta 3 mm, y que potencias medias son más eficaces que altas. El monitoreo de la corriente de RF permite optimizar la potencia aplicada. Finalmente, se continuó trabajando en termocoagulación de zonas epileptógenas (con modelos realistas construidos a partir de imágenes de cerebro), en particular, en heterotopía periventricular. Se concluyó que no se muestra una alteración de la zona de coagulación debido a la proximidad del ventrículo. Se publicaron dos trabajos en revistas internacionales en esta temática y dos trabajos completos en el congreso de la Sociedad Argentina de Bioingeniería (SABI 2025). En la temática de biomecánica, se desarrolló un modelo simplificado por elementos finitos que permite simular condiciones fisiológicas y patológicas del disco intervertebral (cambios en la altura del disco, el volumen del núcleo pulposo y la cantidad de cemento óseo inyectado). El resultado se publicó como trabajo completo en las actas de la Asociación Argentina de Mecánica Computacional. Finalmente, se trabajó en el modelado de la conductividad eléctrica en hueso cortical en función de su microestructura y anisotropía. Este modelo también fue presentado en SABI 2025. </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">5.7.- Dificultades: no se produjeron dificultades en el desarrollo del proyecto.
+    <t xml:space="preserve">5.7.- Dificultades: no se produjeron dificultades en el desarrollo del proyecto.
 </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">5.2.-Código de Proyecto: ENECLP0010122</t>
@@ -412,9 +410,6 @@
     <t xml:space="preserve">María José Cervantes, Catalina A. Cely-Ortíz y Ramiro M. Irastorza</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramiro M. Irastorza</t>
-  </si>
-  <si>
     <t xml:space="preserve">Computer Modeling of Radiofrequency Thermocoagulation in Periventricular Heterotopia- Related Epilepsy</t>
   </si>
   <si>
@@ -702,7 +697,7 @@
     <t xml:space="preserve">YTEC S.A</t>
   </si>
   <si>
-    <t xml:space="preserve">Se realizan modelos computacionales de poblaciones bacterianas con el propósito de predecir velocidades de corrosión en el ámbito de instalaciones de la industria del Oil &amp; Gas.</t>
+    <t xml:space="preserve">Se realizan modelos computacionales de poblaciones bacterianas con el propósito de predecir velocidades de corrosión en el ámbito de instalaciones de la industria del Oil &amp; Gas (Consorcio MIC II).</t>
   </si>
   <si>
     <t xml:space="preserve">V.- INFORME SOBRE RENDICIÓN GENERAL DE CUENTAS</t>
@@ -778,6 +773,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -800,18 +796,21 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1018,11 +1017,11 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1329,7 +1328,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J384"/>
+  <dimension ref="A1:J386"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.67"/>
@@ -1337,14 +1336,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="49.88"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +1353,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1362,7 +1361,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1372,7 +1371,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1382,7 +1381,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
@@ -1392,7 +1391,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1402,7 +1401,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
@@ -1412,7 +1411,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
@@ -1432,7 +1431,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
@@ -1442,7 +1441,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
@@ -1456,7 +1455,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
         <v>1</v>
       </c>
@@ -1470,7 +1469,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>2</v>
       </c>
@@ -1484,7 +1483,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>3</v>
       </c>
@@ -1498,7 +1497,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
         <v>4</v>
       </c>
@@ -1512,7 +1511,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1530,7 +1529,7 @@
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -1538,7 +1537,7 @@
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -1546,7 +1545,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -1554,7 +1553,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -1562,7 +1561,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -1570,7 +1569,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -1578,7 +1577,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -1596,7 +1595,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -1604,7 +1603,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -1612,7 +1611,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -1620,7 +1619,7 @@
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -1628,7 +1627,7 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -1636,7 +1635,7 @@
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
@@ -1644,7 +1643,7 @@
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1652,7 +1651,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
         <v>22</v>
       </c>
@@ -1662,7 +1661,7 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
         <v>23</v>
       </c>
@@ -1672,7 +1671,7 @@
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
         <v>9</v>
       </c>
@@ -1692,163 +1691,177 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6" t="s">
+      <c r="D36" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="E36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" s="0" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="0"/>
+      <c r="D37" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="0" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>33</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="n">
-        <v>4</v>
-      </c>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6"/>
       <c r="B39" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D39" s="6"/>
+        <v>37</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="E39" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="D40" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="E40" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="E41" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="6"/>
+      <c r="B42" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="C42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+      <c r="D42" s="6"/>
+      <c r="E42" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B45" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C45" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>15</v>
+      </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1856,51 +1869,50 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
-        <v>41</v>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
-    </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-    </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="n">
-        <v>1</v>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-    </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -1908,9 +1920,9 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -1918,489 +1930,483 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
-        <v>42</v>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-    </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B60" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58" s="6" t="s">
+      <c r="C60" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="n">
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B61" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D59" s="6" t="n">
+      <c r="C61" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D61" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="n">
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D60" s="6" t="n">
+      <c r="B62" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D62" s="6" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="n">
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D61" s="6" t="n">
+      <c r="B63" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" s="6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="n">
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-    </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="n">
-        <v>1</v>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-    </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="s">
-        <v>52</v>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
       <c r="D71" s="6"/>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="n">
-        <v>1</v>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
       <c r="D73" s="6"/>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-    </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
       <c r="D76" s="6"/>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6" t="s">
-        <v>53</v>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
       <c r="D78" s="6"/>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6" t="s">
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B81" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D80" s="6" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D81" s="6" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D81" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B82" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="D82" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D83" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6" t="s">
-        <v>37</v>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="B84" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="D84" s="6" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-    </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="6" t="n">
-        <v>1</v>
+      <c r="C86" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
       <c r="D88" s="6"/>
     </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-    </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
       <c r="D90" s="6"/>
     </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
       <c r="D91" s="6"/>
     </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-    </row>
-    <row r="94" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="6" t="s">
+    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+    </row>
+    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+    </row>
+    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B94" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D94" s="11" t="s">
+      <c r="B96" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E94" s="12" t="s">
+      <c r="C96" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F94" s="12"/>
-    </row>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6" t="n">
+      <c r="D96" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F96" s="12"/>
+    </row>
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B95" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C95" s="13" t="n">
+      <c r="B97" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C97" s="13" t="n">
         <v>45901</v>
       </c>
-      <c r="D95" s="11" t="n">
+      <c r="D97" s="11" t="n">
         <v>665085</v>
       </c>
-      <c r="E95" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F95" s="12"/>
-    </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6" t="n">
+      <c r="E97" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F97" s="12"/>
+    </row>
+    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B96" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C96" s="13" t="n">
+      <c r="B98" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C98" s="13" t="n">
         <v>45870</v>
       </c>
-      <c r="D96" s="11" t="n">
+      <c r="D98" s="11" t="n">
         <v>1818000</v>
       </c>
-      <c r="E96" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F96" s="12"/>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6" t="n">
+      <c r="E98" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F98" s="12"/>
+    </row>
+    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B97" s="11"/>
-      <c r="C97" s="11"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="12"/>
-      <c r="F97" s="12"/>
-    </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="6" t="n">
+      <c r="B99" s="11"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="12"/>
-      <c r="F98" s="12"/>
-    </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="14"/>
-      <c r="B99" s="14"/>
-      <c r="C99" s="14"/>
-      <c r="D99" s="14"/>
-      <c r="E99" s="14"/>
-      <c r="F99" s="14"/>
-    </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B100" s="15"/>
-      <c r="C100" s="15"/>
-      <c r="D100" s="15"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
-    </row>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="s">
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+    </row>
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="14"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="14"/>
+      <c r="E101" s="14"/>
+      <c r="F101" s="14"/>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B102" s="15"/>
+      <c r="C102" s="15"/>
+      <c r="D102" s="15"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="15"/>
+    </row>
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B101" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D101" s="11" t="s">
+      <c r="B103" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E101" s="11" t="s">
+      <c r="C103" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="F101" s="11"/>
-    </row>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="6" t="n">
+      <c r="D103" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E103" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F103" s="11"/>
+    </row>
+    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="B102" s="11"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="11"/>
-    </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B103" s="11"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="11"/>
-    </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6" t="n">
-        <v>3</v>
       </c>
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
@@ -2408,9 +2414,9 @@
       <c r="E104" s="11"/>
       <c r="F104" s="11"/>
     </row>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
@@ -2418,55 +2424,55 @@
       <c r="E105" s="11"/>
       <c r="F105" s="11"/>
     </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="9"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="9"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-    </row>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-    </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B108" s="16"/>
-      <c r="C108" s="16"/>
-      <c r="D108" s="16"/>
-      <c r="E108" s="16"/>
-      <c r="F108" s="16"/>
-    </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="6" t="s">
+    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="11"/>
+    </row>
+    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B107" s="11"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="11"/>
+    </row>
+    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="9"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="9"/>
+      <c r="F108" s="9"/>
+    </row>
+    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-    </row>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="6" t="s">
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+    </row>
+    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-    </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="16"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="16"/>
+      <c r="E110" s="16"/>
+      <c r="F110" s="16"/>
+    </row>
+    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
         <v>82</v>
       </c>
@@ -2476,7 +2482,7 @@
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
     </row>
-    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
         <v>83</v>
       </c>
@@ -2486,59 +2492,63 @@
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
     </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="11" t="s">
+    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B113" s="11"/>
-      <c r="C113" s="11"/>
-      <c r="D113" s="11"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="11"/>
-    </row>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="11"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="11"/>
-      <c r="E114" s="11"/>
-      <c r="F114" s="11"/>
-    </row>
-    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="17"/>
-      <c r="B115" s="17"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="17"/>
-      <c r="E115" s="17"/>
-      <c r="F115" s="17"/>
-    </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="10" t="s">
+      <c r="B113" s="6"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+    </row>
+    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B116" s="10"/>
-      <c r="C116" s="10"/>
-      <c r="D116" s="10"/>
-      <c r="E116" s="10"/>
-      <c r="F116" s="10"/>
-    </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="10"/>
-      <c r="B117" s="10"/>
-      <c r="C117" s="10"/>
-      <c r="D117" s="10"/>
-      <c r="E117" s="10"/>
-      <c r="F117" s="10"/>
-    </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="10"/>
+      <c r="B114" s="6"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+    </row>
+    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B115" s="11"/>
+      <c r="C115" s="11"/>
+      <c r="D115" s="11"/>
+      <c r="E115" s="11"/>
+      <c r="F115" s="11"/>
+    </row>
+    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="11"/>
+      <c r="B116" s="11"/>
+      <c r="C116" s="11"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
+      <c r="F116" s="11"/>
+    </row>
+    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="17"/>
+      <c r="B117" s="17"/>
+      <c r="C117" s="17"/>
+      <c r="D117" s="17"/>
+      <c r="E117" s="17"/>
+      <c r="F117" s="17"/>
+    </row>
+    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="10" t="s">
+        <v>87</v>
+      </c>
       <c r="B118" s="10"/>
       <c r="C118" s="10"/>
       <c r="D118" s="10"/>
       <c r="E118" s="10"/>
       <c r="F118" s="10"/>
     </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10"/>
       <c r="B119" s="10"/>
       <c r="C119" s="10"/>
@@ -2546,7 +2556,7 @@
       <c r="E119" s="10"/>
       <c r="F119" s="10"/>
     </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10"/>
       <c r="B120" s="10"/>
       <c r="C120" s="10"/>
@@ -2554,7 +2564,7 @@
       <c r="E120" s="10"/>
       <c r="F120" s="10"/>
     </row>
-    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10"/>
       <c r="B121" s="10"/>
       <c r="C121" s="10"/>
@@ -2562,41 +2572,41 @@
       <c r="E121" s="10"/>
       <c r="F121" s="10"/>
     </row>
-    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="3"/>
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
-    </row>
-    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="10" t="s">
-        <v>86</v>
-      </c>
+    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="10"/>
+      <c r="B122" s="10"/>
+      <c r="C122" s="10"/>
+      <c r="D122" s="10"/>
+      <c r="E122" s="10"/>
+      <c r="F122" s="10"/>
+    </row>
+    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="10"/>
       <c r="B123" s="10"/>
       <c r="C123" s="10"/>
       <c r="D123" s="10"/>
       <c r="E123" s="10"/>
       <c r="F123" s="10"/>
     </row>
-    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="10"/>
-      <c r="B124" s="10"/>
-      <c r="C124" s="10"/>
-      <c r="D124" s="10"/>
-      <c r="E124" s="10"/>
-      <c r="F124" s="10"/>
-    </row>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="10"/>
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+    </row>
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="10" t="s">
+        <v>88</v>
+      </c>
       <c r="B125" s="10"/>
       <c r="C125" s="10"/>
       <c r="D125" s="10"/>
       <c r="E125" s="10"/>
       <c r="F125" s="10"/>
     </row>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10"/>
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
@@ -2604,7 +2614,7 @@
       <c r="E126" s="10"/>
       <c r="F126" s="10"/>
     </row>
-    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10"/>
       <c r="B127" s="10"/>
       <c r="C127" s="10"/>
@@ -2612,41 +2622,41 @@
       <c r="E127" s="10"/>
       <c r="F127" s="10"/>
     </row>
-    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="17"/>
-      <c r="B128" s="17"/>
-      <c r="C128" s="17"/>
-      <c r="D128" s="17"/>
-      <c r="E128" s="17"/>
-      <c r="F128" s="17"/>
-    </row>
-    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B129" s="18"/>
-      <c r="C129" s="18"/>
-      <c r="D129" s="18"/>
-      <c r="E129" s="18"/>
-      <c r="F129" s="18"/>
-    </row>
-    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="18"/>
-      <c r="B130" s="18"/>
-      <c r="C130" s="18"/>
-      <c r="D130" s="18"/>
-      <c r="E130" s="18"/>
-      <c r="F130" s="18"/>
-    </row>
-    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="18"/>
+    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="10"/>
+      <c r="B128" s="10"/>
+      <c r="C128" s="10"/>
+      <c r="D128" s="10"/>
+      <c r="E128" s="10"/>
+      <c r="F128" s="10"/>
+    </row>
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="10"/>
+      <c r="B129" s="10"/>
+      <c r="C129" s="10"/>
+      <c r="D129" s="10"/>
+      <c r="E129" s="10"/>
+      <c r="F129" s="10"/>
+    </row>
+    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="17"/>
+      <c r="B130" s="17"/>
+      <c r="C130" s="17"/>
+      <c r="D130" s="17"/>
+      <c r="E130" s="17"/>
+      <c r="F130" s="17"/>
+    </row>
+    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="18" t="s">
+        <v>89</v>
+      </c>
       <c r="B131" s="18"/>
       <c r="C131" s="18"/>
       <c r="D131" s="18"/>
       <c r="E131" s="18"/>
       <c r="F131" s="18"/>
     </row>
-    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="18"/>
       <c r="B132" s="18"/>
       <c r="C132" s="18"/>
@@ -2654,61 +2664,57 @@
       <c r="E132" s="18"/>
       <c r="F132" s="18"/>
     </row>
-    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="17"/>
-      <c r="B133" s="17"/>
-      <c r="C133" s="17"/>
-      <c r="D133" s="17"/>
-      <c r="E133" s="17"/>
-      <c r="F133" s="17"/>
-    </row>
-    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="11"/>
-      <c r="E134" s="11"/>
-      <c r="F134" s="11"/>
-    </row>
-    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="11"/>
-      <c r="B135" s="11"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="11"/>
-      <c r="F135" s="11"/>
-    </row>
-    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="19"/>
-      <c r="B136" s="19"/>
-      <c r="C136" s="19"/>
-      <c r="D136" s="19"/>
-      <c r="E136" s="19"/>
-      <c r="F136" s="19"/>
-    </row>
-    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-    </row>
-    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-    </row>
-    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="18"/>
+      <c r="B133" s="18"/>
+      <c r="C133" s="18"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="18"/>
+    </row>
+    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="18"/>
+      <c r="B134" s="18"/>
+      <c r="C134" s="18"/>
+      <c r="D134" s="18"/>
+      <c r="E134" s="18"/>
+      <c r="F134" s="18"/>
+    </row>
+    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="17"/>
+      <c r="B135" s="17"/>
+      <c r="C135" s="17"/>
+      <c r="D135" s="17"/>
+      <c r="E135" s="17"/>
+      <c r="F135" s="17"/>
+    </row>
+    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B136" s="11"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
+      <c r="F136" s="11"/>
+    </row>
+    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="11"/>
+      <c r="B137" s="11"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="11"/>
+      <c r="E137" s="11"/>
+      <c r="F137" s="11"/>
+    </row>
+    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="19"/>
+      <c r="B138" s="19"/>
+      <c r="C138" s="19"/>
+      <c r="D138" s="19"/>
+      <c r="E138" s="19"/>
+      <c r="F138" s="19"/>
+    </row>
+    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="6" t="s">
         <v>83</v>
       </c>
@@ -2718,59 +2724,63 @@
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
     </row>
-    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B140" s="20"/>
-      <c r="C140" s="20"/>
-      <c r="D140" s="20"/>
-      <c r="E140" s="20"/>
-      <c r="F140" s="20"/>
-    </row>
-    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="20"/>
-      <c r="B141" s="20"/>
-      <c r="C141" s="20"/>
-      <c r="D141" s="20"/>
-      <c r="E141" s="20"/>
-      <c r="F141" s="20"/>
-    </row>
-    <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="17"/>
-      <c r="B142" s="17"/>
-      <c r="C142" s="17"/>
-      <c r="D142" s="17"/>
-      <c r="E142" s="17"/>
-      <c r="F142" s="17"/>
-    </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="10" t="s">
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B143" s="10"/>
-      <c r="C143" s="10"/>
-      <c r="D143" s="10"/>
-      <c r="E143" s="10"/>
-      <c r="F143" s="10"/>
-    </row>
-    <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="10"/>
-      <c r="B144" s="10"/>
-      <c r="C144" s="10"/>
-      <c r="D144" s="10"/>
-      <c r="E144" s="10"/>
-      <c r="F144" s="10"/>
-    </row>
-    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="10"/>
+      <c r="B140" s="6"/>
+      <c r="C140" s="6"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="6"/>
+    </row>
+    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B141" s="6"/>
+      <c r="C141" s="6"/>
+      <c r="D141" s="6"/>
+      <c r="E141" s="6"/>
+      <c r="F141" s="6"/>
+    </row>
+    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B142" s="20"/>
+      <c r="C142" s="20"/>
+      <c r="D142" s="20"/>
+      <c r="E142" s="20"/>
+      <c r="F142" s="20"/>
+    </row>
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="20"/>
+      <c r="B143" s="20"/>
+      <c r="C143" s="20"/>
+      <c r="D143" s="20"/>
+      <c r="E143" s="20"/>
+      <c r="F143" s="20"/>
+    </row>
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="17"/>
+      <c r="B144" s="17"/>
+      <c r="C144" s="17"/>
+      <c r="D144" s="17"/>
+      <c r="E144" s="17"/>
+      <c r="F144" s="17"/>
+    </row>
+    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="B145" s="10"/>
       <c r="C145" s="10"/>
       <c r="D145" s="10"/>
       <c r="E145" s="10"/>
       <c r="F145" s="10"/>
     </row>
-    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="10"/>
@@ -2778,7 +2788,7 @@
       <c r="E146" s="10"/>
       <c r="F146" s="10"/>
     </row>
-    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="10"/>
@@ -2786,7 +2796,7 @@
       <c r="E147" s="10"/>
       <c r="F147" s="10"/>
     </row>
-    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="10"/>
       <c r="B148" s="10"/>
       <c r="C148" s="10"/>
@@ -2794,41 +2804,41 @@
       <c r="E148" s="10"/>
       <c r="F148" s="10"/>
     </row>
-    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="3"/>
-      <c r="B149" s="3"/>
-      <c r="C149" s="3"/>
-      <c r="D149" s="3"/>
-      <c r="E149" s="3"/>
-      <c r="F149" s="3"/>
-    </row>
-    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="B150" s="21"/>
-      <c r="C150" s="21"/>
-      <c r="D150" s="21"/>
-      <c r="E150" s="21"/>
-      <c r="F150" s="21"/>
-    </row>
-    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="21"/>
-      <c r="B151" s="21"/>
-      <c r="C151" s="21"/>
-      <c r="D151" s="21"/>
-      <c r="E151" s="21"/>
-      <c r="F151" s="21"/>
-    </row>
-    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="21"/>
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="10"/>
+      <c r="B149" s="10"/>
+      <c r="C149" s="10"/>
+      <c r="D149" s="10"/>
+      <c r="E149" s="10"/>
+      <c r="F149" s="10"/>
+    </row>
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="10"/>
+      <c r="B150" s="10"/>
+      <c r="C150" s="10"/>
+      <c r="D150" s="10"/>
+      <c r="E150" s="10"/>
+      <c r="F150" s="10"/>
+    </row>
+    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3"/>
+    </row>
+    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="B152" s="21"/>
       <c r="C152" s="21"/>
       <c r="D152" s="21"/>
       <c r="E152" s="21"/>
       <c r="F152" s="21"/>
     </row>
-    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="21"/>
       <c r="B153" s="21"/>
       <c r="C153" s="21"/>
@@ -2836,7 +2846,7 @@
       <c r="E153" s="21"/>
       <c r="F153" s="21"/>
     </row>
-    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="21"/>
       <c r="B154" s="21"/>
       <c r="C154" s="21"/>
@@ -2844,41 +2854,41 @@
       <c r="E154" s="21"/>
       <c r="F154" s="21"/>
     </row>
-    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="17"/>
-      <c r="B155" s="17"/>
-      <c r="C155" s="17"/>
-      <c r="D155" s="17"/>
-      <c r="E155" s="17"/>
-      <c r="F155" s="17"/>
-    </row>
-    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="21" t="s">
-        <v>93</v>
-      </c>
+    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="21"/>
+      <c r="B155" s="21"/>
+      <c r="C155" s="21"/>
+      <c r="D155" s="21"/>
+      <c r="E155" s="21"/>
+      <c r="F155" s="21"/>
+    </row>
+    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="21"/>
       <c r="B156" s="21"/>
       <c r="C156" s="21"/>
       <c r="D156" s="21"/>
       <c r="E156" s="21"/>
       <c r="F156" s="21"/>
     </row>
-    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="21"/>
-      <c r="B157" s="21"/>
-      <c r="C157" s="21"/>
-      <c r="D157" s="21"/>
-      <c r="E157" s="21"/>
-      <c r="F157" s="21"/>
-    </row>
-    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="21"/>
+    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="17"/>
+      <c r="B157" s="17"/>
+      <c r="C157" s="17"/>
+      <c r="D157" s="17"/>
+      <c r="E157" s="17"/>
+      <c r="F157" s="17"/>
+    </row>
+    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="B158" s="21"/>
       <c r="C158" s="21"/>
       <c r="D158" s="21"/>
       <c r="E158" s="21"/>
       <c r="F158" s="21"/>
     </row>
-    <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="21"/>
       <c r="B159" s="21"/>
       <c r="C159" s="21"/>
@@ -2886,63 +2896,59 @@
       <c r="E159" s="21"/>
       <c r="F159" s="21"/>
     </row>
-    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="17"/>
-      <c r="B160" s="17"/>
-      <c r="C160" s="17"/>
-      <c r="D160" s="17"/>
-      <c r="E160" s="17"/>
-      <c r="F160" s="17"/>
-    </row>
-    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B161" s="11"/>
-      <c r="C161" s="11"/>
-      <c r="D161" s="11"/>
-      <c r="E161" s="11"/>
-      <c r="F161" s="11"/>
-    </row>
-    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="11"/>
-      <c r="B162" s="11"/>
-      <c r="C162" s="11"/>
-      <c r="D162" s="11"/>
-      <c r="E162" s="11"/>
-      <c r="F162" s="11"/>
-    </row>
-    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="9"/>
-      <c r="B163" s="9"/>
-      <c r="C163" s="9"/>
-      <c r="D163" s="9"/>
-      <c r="E163" s="9"/>
-      <c r="F163" s="9"/>
-    </row>
-    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B164" s="6"/>
-      <c r="C164" s="6"/>
-      <c r="D164" s="6"/>
-      <c r="E164" s="6"/>
-      <c r="F164" s="6"/>
-    </row>
-    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B165" s="6"/>
-      <c r="C165" s="6"/>
-      <c r="D165" s="6"/>
-      <c r="E165" s="6"/>
-      <c r="F165" s="6"/>
-    </row>
-    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="21"/>
+      <c r="B160" s="21"/>
+      <c r="C160" s="21"/>
+      <c r="D160" s="21"/>
+      <c r="E160" s="21"/>
+      <c r="F160" s="21"/>
+    </row>
+    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="21"/>
+      <c r="B161" s="21"/>
+      <c r="C161" s="21"/>
+      <c r="D161" s="21"/>
+      <c r="E161" s="21"/>
+      <c r="F161" s="21"/>
+    </row>
+    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="17"/>
+      <c r="B162" s="17"/>
+      <c r="C162" s="17"/>
+      <c r="D162" s="17"/>
+      <c r="E162" s="17"/>
+      <c r="F162" s="17"/>
+    </row>
+    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B163" s="11"/>
+      <c r="C163" s="11"/>
+      <c r="D163" s="11"/>
+      <c r="E163" s="11"/>
+      <c r="F163" s="11"/>
+    </row>
+    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="11"/>
+      <c r="B164" s="11"/>
+      <c r="C164" s="11"/>
+      <c r="D164" s="11"/>
+      <c r="E164" s="11"/>
+      <c r="F164" s="11"/>
+    </row>
+    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="9"/>
+      <c r="B165" s="9"/>
+      <c r="C165" s="9"/>
+      <c r="D165" s="9"/>
+      <c r="E165" s="9"/>
+      <c r="F165" s="9"/>
+    </row>
+    <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="6" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
@@ -2950,59 +2956,63 @@
       <c r="E166" s="6"/>
       <c r="F166" s="6"/>
     </row>
-    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="10" t="s">
+    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B167" s="10"/>
-      <c r="C167" s="10"/>
-      <c r="D167" s="10"/>
-      <c r="E167" s="10"/>
-      <c r="F167" s="10"/>
-    </row>
-    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="10"/>
-      <c r="B168" s="10"/>
-      <c r="C168" s="10"/>
-      <c r="D168" s="10"/>
-      <c r="E168" s="10"/>
-      <c r="F168" s="10"/>
-    </row>
-    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="17"/>
-      <c r="B169" s="17"/>
-      <c r="C169" s="17"/>
-      <c r="D169" s="17"/>
-      <c r="E169" s="17"/>
-      <c r="F169" s="17"/>
-    </row>
-    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="10" t="s">
+      <c r="B167" s="6"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="6"/>
+      <c r="E167" s="6"/>
+      <c r="F167" s="6"/>
+    </row>
+    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="6" t="s">
         <v>97</v>
       </c>
+      <c r="B168" s="6"/>
+      <c r="C168" s="6"/>
+      <c r="D168" s="6"/>
+      <c r="E168" s="6"/>
+      <c r="F168" s="6"/>
+    </row>
+    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A169" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B169" s="10"/>
+      <c r="C169" s="10"/>
+      <c r="D169" s="10"/>
+      <c r="E169" s="10"/>
+      <c r="F169" s="10"/>
+    </row>
+    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="10"/>
       <c r="B170" s="10"/>
       <c r="C170" s="10"/>
       <c r="D170" s="10"/>
       <c r="E170" s="10"/>
       <c r="F170" s="10"/>
     </row>
-    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="10"/>
-      <c r="B171" s="10"/>
-      <c r="C171" s="10"/>
-      <c r="D171" s="10"/>
-      <c r="E171" s="10"/>
-      <c r="F171" s="10"/>
-    </row>
-    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="10"/>
+    <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="17"/>
+      <c r="B171" s="17"/>
+      <c r="C171" s="17"/>
+      <c r="D171" s="17"/>
+      <c r="E171" s="17"/>
+      <c r="F171" s="17"/>
+    </row>
+    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="10" t="s">
+        <v>99</v>
+      </c>
       <c r="B172" s="10"/>
       <c r="C172" s="10"/>
       <c r="D172" s="10"/>
       <c r="E172" s="10"/>
       <c r="F172" s="10"/>
     </row>
-    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="10"/>
       <c r="B173" s="10"/>
       <c r="C173" s="10"/>
@@ -3010,7 +3020,7 @@
       <c r="E173" s="10"/>
       <c r="F173" s="10"/>
     </row>
-    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="10"/>
       <c r="B174" s="10"/>
       <c r="C174" s="10"/>
@@ -3018,7 +3028,7 @@
       <c r="E174" s="10"/>
       <c r="F174" s="10"/>
     </row>
-    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="10"/>
       <c r="B175" s="10"/>
       <c r="C175" s="10"/>
@@ -3026,41 +3036,41 @@
       <c r="E175" s="10"/>
       <c r="F175" s="10"/>
     </row>
-    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="3"/>
-      <c r="B176" s="3"/>
-      <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
-      <c r="E176" s="3"/>
-      <c r="F176" s="3"/>
-    </row>
-    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="10" t="s">
-        <v>98</v>
-      </c>
+    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="10"/>
+      <c r="B176" s="10"/>
+      <c r="C176" s="10"/>
+      <c r="D176" s="10"/>
+      <c r="E176" s="10"/>
+      <c r="F176" s="10"/>
+    </row>
+    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="10"/>
       <c r="B177" s="10"/>
       <c r="C177" s="10"/>
       <c r="D177" s="10"/>
       <c r="E177" s="10"/>
       <c r="F177" s="10"/>
     </row>
-    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="10"/>
-      <c r="B178" s="10"/>
-      <c r="C178" s="10"/>
-      <c r="D178" s="10"/>
-      <c r="E178" s="10"/>
-      <c r="F178" s="10"/>
-    </row>
-    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="10"/>
+    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+      <c r="F178" s="3"/>
+    </row>
+    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A179" s="10" t="s">
+        <v>100</v>
+      </c>
       <c r="B179" s="10"/>
       <c r="C179" s="10"/>
       <c r="D179" s="10"/>
       <c r="E179" s="10"/>
       <c r="F179" s="10"/>
     </row>
-    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="10"/>
       <c r="B180" s="10"/>
       <c r="C180" s="10"/>
@@ -3068,7 +3078,7 @@
       <c r="E180" s="10"/>
       <c r="F180" s="10"/>
     </row>
-    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="10"/>
       <c r="B181" s="10"/>
       <c r="C181" s="10"/>
@@ -3076,41 +3086,41 @@
       <c r="E181" s="10"/>
       <c r="F181" s="10"/>
     </row>
-    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="17"/>
-      <c r="B182" s="17"/>
-      <c r="C182" s="17"/>
-      <c r="D182" s="17"/>
-      <c r="E182" s="17"/>
-      <c r="F182" s="17"/>
-    </row>
-    <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B183" s="11"/>
-      <c r="C183" s="11"/>
-      <c r="D183" s="11"/>
-      <c r="E183" s="11"/>
-      <c r="F183" s="11"/>
-    </row>
-    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="11"/>
-      <c r="B184" s="11"/>
-      <c r="C184" s="11"/>
-      <c r="D184" s="11"/>
-      <c r="E184" s="11"/>
-      <c r="F184" s="11"/>
-    </row>
-    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="11"/>
+    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="10"/>
+      <c r="B182" s="10"/>
+      <c r="C182" s="10"/>
+      <c r="D182" s="10"/>
+      <c r="E182" s="10"/>
+      <c r="F182" s="10"/>
+    </row>
+    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="10"/>
+      <c r="B183" s="10"/>
+      <c r="C183" s="10"/>
+      <c r="D183" s="10"/>
+      <c r="E183" s="10"/>
+      <c r="F183" s="10"/>
+    </row>
+    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="17"/>
+      <c r="B184" s="17"/>
+      <c r="C184" s="17"/>
+      <c r="D184" s="17"/>
+      <c r="E184" s="17"/>
+      <c r="F184" s="17"/>
+    </row>
+    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="11" t="s">
+        <v>101</v>
+      </c>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
       <c r="D185" s="11"/>
       <c r="E185" s="11"/>
       <c r="F185" s="11"/>
     </row>
-    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="11"/>
       <c r="B186" s="11"/>
       <c r="C186" s="11"/>
@@ -3118,63 +3128,59 @@
       <c r="E186" s="11"/>
       <c r="F186" s="11"/>
     </row>
-    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="17"/>
-      <c r="B187" s="17"/>
-      <c r="C187" s="17"/>
-      <c r="D187" s="17"/>
-      <c r="E187" s="17"/>
-      <c r="F187" s="17"/>
-    </row>
-    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="11" t="s">
-        <v>88</v>
-      </c>
+    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="11"/>
+      <c r="B187" s="11"/>
+      <c r="C187" s="11"/>
+      <c r="D187" s="11"/>
+      <c r="E187" s="11"/>
+      <c r="F187" s="11"/>
+    </row>
+    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="11"/>
       <c r="B188" s="11"/>
       <c r="C188" s="11"/>
       <c r="D188" s="11"/>
       <c r="E188" s="11"/>
       <c r="F188" s="11"/>
     </row>
-    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="11"/>
-      <c r="B189" s="11"/>
-      <c r="C189" s="11"/>
-      <c r="D189" s="11"/>
-      <c r="E189" s="11"/>
-      <c r="F189" s="11"/>
-    </row>
-    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="9"/>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
-      <c r="D190" s="9"/>
-      <c r="E190" s="9"/>
-      <c r="F190" s="9"/>
-    </row>
-    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B191" s="6"/>
-      <c r="C191" s="6"/>
-      <c r="D191" s="6"/>
-      <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
-    </row>
-    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="B192" s="22"/>
-      <c r="C192" s="22"/>
-      <c r="D192" s="22"/>
-      <c r="E192" s="22"/>
-      <c r="F192" s="22"/>
-    </row>
-    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="17"/>
+      <c r="B189" s="17"/>
+      <c r="C189" s="17"/>
+      <c r="D189" s="17"/>
+      <c r="E189" s="17"/>
+      <c r="F189" s="17"/>
+    </row>
+    <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B190" s="11"/>
+      <c r="C190" s="11"/>
+      <c r="D190" s="11"/>
+      <c r="E190" s="11"/>
+      <c r="F190" s="11"/>
+    </row>
+    <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="11"/>
+      <c r="B191" s="11"/>
+      <c r="C191" s="11"/>
+      <c r="D191" s="11"/>
+      <c r="E191" s="11"/>
+      <c r="F191" s="11"/>
+    </row>
+    <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="9"/>
+      <c r="B192" s="9"/>
+      <c r="C192" s="9"/>
+      <c r="D192" s="9"/>
+      <c r="E192" s="9"/>
+      <c r="F192" s="9"/>
+    </row>
+    <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="6" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
@@ -3182,59 +3188,63 @@
       <c r="E193" s="6"/>
       <c r="F193" s="6"/>
     </row>
-    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B194" s="10"/>
-      <c r="C194" s="10"/>
-      <c r="D194" s="10"/>
-      <c r="E194" s="10"/>
-      <c r="F194" s="10"/>
-    </row>
-    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="10"/>
-      <c r="B195" s="10"/>
-      <c r="C195" s="10"/>
-      <c r="D195" s="10"/>
-      <c r="E195" s="10"/>
-      <c r="F195" s="10"/>
-    </row>
-    <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="17"/>
-      <c r="B196" s="17"/>
-      <c r="C196" s="17"/>
-      <c r="D196" s="17"/>
-      <c r="E196" s="17"/>
-      <c r="F196" s="17"/>
-    </row>
-    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="10" t="s">
+    <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="22" t="s">
         <v>102</v>
       </c>
+      <c r="B194" s="22"/>
+      <c r="C194" s="22"/>
+      <c r="D194" s="22"/>
+      <c r="E194" s="22"/>
+      <c r="F194" s="22"/>
+    </row>
+    <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B195" s="6"/>
+      <c r="C195" s="6"/>
+      <c r="D195" s="6"/>
+      <c r="E195" s="6"/>
+      <c r="F195" s="6"/>
+    </row>
+    <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A196" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B196" s="10"/>
+      <c r="C196" s="10"/>
+      <c r="D196" s="10"/>
+      <c r="E196" s="10"/>
+      <c r="F196" s="10"/>
+    </row>
+    <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="10"/>
       <c r="B197" s="10"/>
       <c r="C197" s="10"/>
       <c r="D197" s="10"/>
       <c r="E197" s="10"/>
       <c r="F197" s="10"/>
     </row>
-    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="10"/>
-      <c r="B198" s="10"/>
-      <c r="C198" s="10"/>
-      <c r="D198" s="10"/>
-      <c r="E198" s="10"/>
-      <c r="F198" s="10"/>
-    </row>
-    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="10"/>
+    <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="17"/>
+      <c r="B198" s="17"/>
+      <c r="C198" s="17"/>
+      <c r="D198" s="17"/>
+      <c r="E198" s="17"/>
+      <c r="F198" s="17"/>
+    </row>
+    <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A199" s="10" t="s">
+        <v>104</v>
+      </c>
       <c r="B199" s="10"/>
       <c r="C199" s="10"/>
       <c r="D199" s="10"/>
       <c r="E199" s="10"/>
       <c r="F199" s="10"/>
     </row>
-    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="10"/>
       <c r="B200" s="10"/>
       <c r="C200" s="10"/>
@@ -3242,7 +3252,7 @@
       <c r="E200" s="10"/>
       <c r="F200" s="10"/>
     </row>
-    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="10"/>
       <c r="B201" s="10"/>
       <c r="C201" s="10"/>
@@ -3259,33 +3269,33 @@
       <c r="F202" s="10"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="3"/>
-      <c r="B203" s="3"/>
-      <c r="C203" s="3"/>
-      <c r="D203" s="3"/>
-      <c r="E203" s="3"/>
-      <c r="F203" s="3"/>
-    </row>
-    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B204" s="21"/>
-      <c r="C204" s="21"/>
-      <c r="D204" s="21"/>
-      <c r="E204" s="21"/>
-      <c r="F204" s="21"/>
+      <c r="A203" s="10"/>
+      <c r="B203" s="10"/>
+      <c r="C203" s="10"/>
+      <c r="D203" s="10"/>
+      <c r="E203" s="10"/>
+      <c r="F203" s="10"/>
+    </row>
+    <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="10"/>
+      <c r="B204" s="10"/>
+      <c r="C204" s="10"/>
+      <c r="D204" s="10"/>
+      <c r="E204" s="10"/>
+      <c r="F204" s="10"/>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="21"/>
-      <c r="B205" s="21"/>
-      <c r="C205" s="21"/>
-      <c r="D205" s="21"/>
-      <c r="E205" s="21"/>
-      <c r="F205" s="21"/>
-    </row>
-    <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="21"/>
+      <c r="A205" s="3"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="3"/>
+      <c r="F205" s="3"/>
+    </row>
+    <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A206" s="21" t="s">
+        <v>105</v>
+      </c>
       <c r="B206" s="21"/>
       <c r="C206" s="21"/>
       <c r="D206" s="21"/>
@@ -3309,33 +3319,33 @@
       <c r="F208" s="21"/>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="17"/>
-      <c r="B209" s="17"/>
-      <c r="C209" s="17"/>
-      <c r="D209" s="17"/>
-      <c r="E209" s="17"/>
-      <c r="F209" s="17"/>
+      <c r="A209" s="21"/>
+      <c r="B209" s="21"/>
+      <c r="C209" s="21"/>
+      <c r="D209" s="21"/>
+      <c r="E209" s="21"/>
+      <c r="F209" s="21"/>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B210" s="11"/>
-      <c r="C210" s="11"/>
-      <c r="D210" s="11"/>
-      <c r="E210" s="11"/>
-      <c r="F210" s="11"/>
+      <c r="A210" s="21"/>
+      <c r="B210" s="21"/>
+      <c r="C210" s="21"/>
+      <c r="D210" s="21"/>
+      <c r="E210" s="21"/>
+      <c r="F210" s="21"/>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="11"/>
-      <c r="B211" s="11"/>
-      <c r="C211" s="11"/>
-      <c r="D211" s="11"/>
-      <c r="E211" s="11"/>
-      <c r="F211" s="11"/>
+      <c r="A211" s="17"/>
+      <c r="B211" s="17"/>
+      <c r="C211" s="17"/>
+      <c r="D211" s="17"/>
+      <c r="E211" s="17"/>
+      <c r="F211" s="17"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="11"/>
+      <c r="A212" s="11" t="s">
+        <v>106</v>
+      </c>
       <c r="B212" s="11"/>
       <c r="C212" s="11"/>
       <c r="D212" s="11"/>
@@ -3351,17 +3361,15 @@
       <c r="F213" s="11"/>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="17"/>
-      <c r="B214" s="17"/>
-      <c r="C214" s="17"/>
-      <c r="D214" s="17"/>
-      <c r="E214" s="17"/>
-      <c r="F214" s="17"/>
+      <c r="A214" s="11"/>
+      <c r="B214" s="11"/>
+      <c r="C214" s="11"/>
+      <c r="D214" s="11"/>
+      <c r="E214" s="11"/>
+      <c r="F214" s="11"/>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="11" t="s">
-        <v>88</v>
-      </c>
+      <c r="A215" s="11"/>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
       <c r="D215" s="11"/>
@@ -3369,28 +3377,30 @@
       <c r="F215" s="11"/>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="11"/>
-      <c r="B216" s="11"/>
-      <c r="C216" s="11"/>
-      <c r="D216" s="11"/>
-      <c r="E216" s="11"/>
-      <c r="F216" s="11"/>
+      <c r="A216" s="17"/>
+      <c r="B216" s="17"/>
+      <c r="C216" s="17"/>
+      <c r="D216" s="17"/>
+      <c r="E216" s="17"/>
+      <c r="F216" s="17"/>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="9"/>
-      <c r="B217" s="9"/>
-      <c r="C217" s="9"/>
-      <c r="D217" s="9"/>
-      <c r="E217" s="9"/>
-      <c r="F217" s="9"/>
+      <c r="A217" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B217" s="11"/>
+      <c r="C217" s="11"/>
+      <c r="D217" s="11"/>
+      <c r="E217" s="11"/>
+      <c r="F217" s="11"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="9"/>
-      <c r="B218" s="9"/>
-      <c r="C218" s="9"/>
-      <c r="D218" s="9"/>
-      <c r="E218" s="9"/>
-      <c r="F218" s="9"/>
+      <c r="A218" s="11"/>
+      <c r="B218" s="11"/>
+      <c r="C218" s="11"/>
+      <c r="D218" s="11"/>
+      <c r="E218" s="11"/>
+      <c r="F218" s="11"/>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="9"/>
@@ -3408,36 +3418,36 @@
       <c r="E220" s="9"/>
       <c r="F220" s="9"/>
     </row>
-    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A221" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="B221" s="23"/>
-      <c r="C221" s="23"/>
-      <c r="D221" s="23"/>
-      <c r="E221" s="23"/>
-      <c r="F221" s="23"/>
+    <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="9"/>
+      <c r="B221" s="9"/>
+      <c r="C221" s="9"/>
+      <c r="D221" s="9"/>
+      <c r="E221" s="9"/>
+      <c r="F221" s="9"/>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B222" s="11"/>
-      <c r="C222" s="11"/>
-      <c r="D222" s="11"/>
-      <c r="E222" s="11"/>
-      <c r="F222" s="11"/>
-    </row>
-    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="11"/>
-      <c r="B223" s="11"/>
-      <c r="C223" s="11"/>
-      <c r="D223" s="11"/>
-      <c r="E223" s="11"/>
-      <c r="F223" s="11"/>
+      <c r="A222" s="9"/>
+      <c r="B222" s="9"/>
+      <c r="C222" s="9"/>
+      <c r="D222" s="9"/>
+      <c r="E222" s="9"/>
+      <c r="F222" s="9"/>
+    </row>
+    <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A223" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B223" s="23"/>
+      <c r="C223" s="23"/>
+      <c r="D223" s="23"/>
+      <c r="E223" s="23"/>
+      <c r="F223" s="23"/>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="11"/>
+      <c r="A224" s="11" t="s">
+        <v>108</v>
+      </c>
       <c r="B224" s="11"/>
       <c r="C224" s="11"/>
       <c r="D224" s="11"/>
@@ -3445,33 +3455,33 @@
       <c r="F224" s="11"/>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="14"/>
-      <c r="B225" s="14"/>
-      <c r="C225" s="14"/>
-      <c r="D225" s="14"/>
-      <c r="E225" s="14"/>
-      <c r="F225" s="14"/>
-    </row>
-    <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A226" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="B226" s="21"/>
-      <c r="C226" s="21"/>
-      <c r="D226" s="21"/>
-      <c r="E226" s="21"/>
-      <c r="F226" s="21"/>
+      <c r="A225" s="11"/>
+      <c r="B225" s="11"/>
+      <c r="C225" s="11"/>
+      <c r="D225" s="11"/>
+      <c r="E225" s="11"/>
+      <c r="F225" s="11"/>
+    </row>
+    <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="11"/>
+      <c r="B226" s="11"/>
+      <c r="C226" s="11"/>
+      <c r="D226" s="11"/>
+      <c r="E226" s="11"/>
+      <c r="F226" s="11"/>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="21"/>
-      <c r="B227" s="21"/>
-      <c r="C227" s="21"/>
-      <c r="D227" s="21"/>
-      <c r="E227" s="21"/>
-      <c r="F227" s="21"/>
-    </row>
-    <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="21"/>
+      <c r="A227" s="14"/>
+      <c r="B227" s="14"/>
+      <c r="C227" s="14"/>
+      <c r="D227" s="14"/>
+      <c r="E227" s="14"/>
+      <c r="F227" s="14"/>
+    </row>
+    <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A228" s="21" t="s">
+        <v>109</v>
+      </c>
       <c r="B228" s="21"/>
       <c r="C228" s="21"/>
       <c r="D228" s="21"/>
@@ -3479,33 +3489,33 @@
       <c r="F228" s="21"/>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="14"/>
-      <c r="B229" s="14"/>
-      <c r="C229" s="14"/>
-      <c r="D229" s="14"/>
-      <c r="E229" s="14"/>
-      <c r="F229" s="14"/>
+      <c r="A229" s="21"/>
+      <c r="B229" s="21"/>
+      <c r="C229" s="21"/>
+      <c r="D229" s="21"/>
+      <c r="E229" s="21"/>
+      <c r="F229" s="21"/>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B230" s="11"/>
-      <c r="C230" s="11"/>
-      <c r="D230" s="11"/>
-      <c r="E230" s="11"/>
-      <c r="F230" s="11"/>
+      <c r="A230" s="21"/>
+      <c r="B230" s="21"/>
+      <c r="C230" s="21"/>
+      <c r="D230" s="21"/>
+      <c r="E230" s="21"/>
+      <c r="F230" s="21"/>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="11"/>
-      <c r="B231" s="11"/>
-      <c r="C231" s="11"/>
-      <c r="D231" s="11"/>
-      <c r="E231" s="11"/>
-      <c r="F231" s="11"/>
+      <c r="A231" s="14"/>
+      <c r="B231" s="14"/>
+      <c r="C231" s="14"/>
+      <c r="D231" s="14"/>
+      <c r="E231" s="14"/>
+      <c r="F231" s="14"/>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="11"/>
+      <c r="A232" s="11" t="s">
+        <v>110</v>
+      </c>
       <c r="B232" s="11"/>
       <c r="C232" s="11"/>
       <c r="D232" s="11"/>
@@ -3521,243 +3531,237 @@
       <c r="F233" s="11"/>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="3"/>
-      <c r="B234" s="3"/>
-      <c r="C234" s="3"/>
-      <c r="D234" s="3"/>
-      <c r="E234" s="3"/>
-      <c r="F234" s="3"/>
-      <c r="G234" s="3"/>
+      <c r="A234" s="11"/>
+      <c r="B234" s="11"/>
+      <c r="C234" s="11"/>
+      <c r="D234" s="11"/>
+      <c r="E234" s="11"/>
+      <c r="F234" s="11"/>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B235" s="4"/>
-      <c r="C235" s="4"/>
-      <c r="D235" s="4"/>
-      <c r="E235" s="4"/>
-      <c r="F235" s="4"/>
-      <c r="G235" s="4"/>
+      <c r="A235" s="11"/>
+      <c r="B235" s="11"/>
+      <c r="C235" s="11"/>
+      <c r="D235" s="11"/>
+      <c r="E235" s="11"/>
+      <c r="F235" s="11"/>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="B236" s="24"/>
-      <c r="C236" s="24"/>
-      <c r="D236" s="24"/>
-      <c r="E236" s="24"/>
-      <c r="F236" s="24"/>
-      <c r="G236" s="24"/>
+      <c r="A236" s="3"/>
+      <c r="B236" s="3"/>
+      <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
+      <c r="E236" s="3"/>
+      <c r="F236" s="3"/>
+      <c r="G236" s="3"/>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="11" t="s">
+      <c r="A237" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B237" s="4"/>
+      <c r="C237" s="4"/>
+      <c r="D237" s="4"/>
+      <c r="E237" s="4"/>
+      <c r="F237" s="4"/>
+      <c r="G237" s="4"/>
+    </row>
+    <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B238" s="24"/>
+      <c r="C238" s="24"/>
+      <c r="D238" s="24"/>
+      <c r="E238" s="24"/>
+      <c r="F238" s="24"/>
+      <c r="G238" s="24"/>
+    </row>
+    <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B237" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C237" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D237" s="11" t="s">
+      <c r="B239" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E237" s="11" t="s">
+      <c r="C239" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="F237" s="11" t="s">
+      <c r="D239" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G237" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="238" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B238" s="25" t="s">
+      <c r="E239" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C238" s="0" t="s">
+      <c r="F239" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D238" s="26" t="n">
-        <v>45944</v>
-      </c>
-      <c r="E238" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="F238" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="G238" s="0" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="239" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B239" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="C239" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="D239" s="26" t="n">
-        <v>45944</v>
-      </c>
-      <c r="E239" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F239" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G239" s="6" t="s">
-        <v>123</v>
+      <c r="G239" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B240" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="C240" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D240" s="26" t="n">
         <v>45944</v>
       </c>
-      <c r="E240" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F240" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="G240" s="6" t="s">
-        <v>126</v>
+      <c r="E240" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B241" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="C241" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="D241" s="26" t="n">
         <v>45944</v>
       </c>
       <c r="E241" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F241" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G241" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B242" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D242" s="26" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E242" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F242" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G242" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F241" s="11" t="s">
+    </row>
+    <row r="243" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B243" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D243" s="26" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E243" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="G241" s="6" t="s">
+      <c r="F243" s="11" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="14"/>
-      <c r="B242" s="14"/>
-      <c r="C242" s="14"/>
-      <c r="D242" s="14"/>
-      <c r="E242" s="14"/>
-      <c r="F242" s="14"/>
-      <c r="G242" s="14"/>
-    </row>
-    <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="11" t="s">
+      <c r="G243" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B243" s="11"/>
-      <c r="C243" s="11"/>
-      <c r="D243" s="11"/>
-      <c r="E243" s="11"/>
-      <c r="F243" s="11"/>
-      <c r="G243" s="11"/>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="27" t="s">
+      <c r="A244" s="14"/>
+      <c r="B244" s="14"/>
+      <c r="C244" s="14"/>
+      <c r="D244" s="14"/>
+      <c r="E244" s="14"/>
+      <c r="F244" s="14"/>
+      <c r="G244" s="14"/>
+    </row>
+    <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B245" s="11"/>
+      <c r="C245" s="11"/>
+      <c r="D245" s="11"/>
+      <c r="E245" s="11"/>
+      <c r="F245" s="11"/>
+      <c r="G245" s="11"/>
+    </row>
+    <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B244" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C244" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="D244" s="27" t="s">
+      <c r="B246" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="E244" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F244" s="27" t="s">
+      <c r="C246" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D246" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="G244" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="H244" s="9"/>
-    </row>
-    <row r="245" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="11" t="n">
+      <c r="E246" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="F246" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="G246" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H246" s="9"/>
+    </row>
+    <row r="247" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B245" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C245" s="11" t="s">
+      <c r="B247" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D245" s="28" t="n">
+      <c r="C247" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D247" s="28" t="n">
         <v>45732</v>
       </c>
-      <c r="E245" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="F245" s="11" t="s">
+      <c r="E247" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G245" s="6" t="s">
+      <c r="F247" s="11" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="11" t="n">
+      <c r="G247" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="B246" s="11"/>
-      <c r="C246" s="11"/>
-      <c r="D246" s="11"/>
-      <c r="E246" s="11"/>
-      <c r="F246" s="11"/>
-      <c r="G246" s="6"/>
-    </row>
-    <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B247" s="11"/>
-      <c r="C247" s="11"/>
-      <c r="D247" s="11"/>
-      <c r="E247" s="11"/>
-      <c r="F247" s="11"/>
-      <c r="G247" s="6"/>
-    </row>
-    <row r="248" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="11" t="n">
-        <v>4</v>
       </c>
       <c r="B248" s="11"/>
       <c r="C248" s="11"/>
@@ -3765,403 +3769,409 @@
       <c r="E248" s="11"/>
       <c r="F248" s="11"/>
       <c r="G248" s="6"/>
-      <c r="H248" s="1"/>
-      <c r="I248" s="1"/>
-      <c r="J248" s="1"/>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="30"/>
-      <c r="B249" s="30"/>
-      <c r="C249" s="30"/>
-      <c r="D249" s="30"/>
-      <c r="E249" s="30"/>
-      <c r="F249" s="30"/>
-      <c r="G249" s="30"/>
-      <c r="H249" s="29"/>
-      <c r="I249" s="29"/>
-      <c r="J249" s="29"/>
-    </row>
-    <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B250" s="4"/>
-      <c r="C250" s="4"/>
-      <c r="D250" s="4"/>
-      <c r="E250" s="4"/>
-      <c r="F250" s="4"/>
-      <c r="G250" s="4"/>
+      <c r="A249" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B249" s="11"/>
+      <c r="C249" s="11"/>
+      <c r="D249" s="11"/>
+      <c r="E249" s="11"/>
+      <c r="F249" s="11"/>
+      <c r="G249" s="6"/>
+    </row>
+    <row r="250" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B250" s="11"/>
+      <c r="C250" s="11"/>
+      <c r="D250" s="11"/>
+      <c r="E250" s="11"/>
+      <c r="F250" s="11"/>
+      <c r="G250" s="6"/>
+      <c r="H250" s="1"/>
+      <c r="I250" s="1"/>
+      <c r="J250" s="1"/>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="11" t="s">
+      <c r="A251" s="30"/>
+      <c r="B251" s="30"/>
+      <c r="C251" s="30"/>
+      <c r="D251" s="30"/>
+      <c r="E251" s="30"/>
+      <c r="F251" s="30"/>
+      <c r="G251" s="30"/>
+      <c r="H251" s="29"/>
+      <c r="I251" s="29"/>
+      <c r="J251" s="29"/>
+    </row>
+    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B251" s="11"/>
-      <c r="C251" s="11"/>
-      <c r="D251" s="11"/>
-      <c r="E251" s="11"/>
-      <c r="F251" s="11"/>
-      <c r="G251" s="11"/>
-    </row>
-    <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="31" t="s">
+      <c r="B252" s="4"/>
+      <c r="C252" s="4"/>
+      <c r="D252" s="4"/>
+      <c r="E252" s="4"/>
+      <c r="F252" s="4"/>
+      <c r="G252" s="4"/>
+    </row>
+    <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B253" s="11"/>
+      <c r="C253" s="11"/>
+      <c r="D253" s="11"/>
+      <c r="E253" s="11"/>
+      <c r="F253" s="11"/>
+      <c r="G253" s="11"/>
+    </row>
+    <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B252" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C252" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D252" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E252" s="11" t="s">
+      <c r="B254" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F252" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="G252" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B253" s="11" t="s">
+      <c r="C254" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D254" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E254" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C253" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D253" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E253" s="25" t="n">
-        <v>10916466</v>
-      </c>
-      <c r="F253" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="G253" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B254" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C254" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D254" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E254" s="11" t="n">
-        <v>21964378</v>
-      </c>
       <c r="F254" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="G254" s="6" t="s">
-        <v>150</v>
+        <v>117</v>
+      </c>
+      <c r="G254" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C255" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D255" s="11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E255" s="25" t="n">
-        <v>15594106</v>
+        <v>10916466</v>
       </c>
       <c r="F255" s="11" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G255" s="6" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B256" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C256" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D256" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E256" s="11" t="n">
+        <v>21964378</v>
+      </c>
+      <c r="F256" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G256" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B257" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C257" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D257" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E257" s="25" t="n">
+        <v>15594106</v>
+      </c>
+      <c r="F257" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G257" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B256" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C256" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D256" s="11" t="s">
+      <c r="B258" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="E256" s="25" t="n">
+      <c r="C258" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D258" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E258" s="25" t="n">
         <v>23065354</v>
       </c>
-      <c r="F256" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="G256" s="6" t="s">
+      <c r="F258" s="11" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B257" s="11" t="s">
+      <c r="G258" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C257" s="11" t="s">
+    </row>
+    <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B259" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D257" s="11" t="s">
+      <c r="C259" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="E257" s="25" t="n">
+      <c r="D259" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E259" s="25" t="n">
         <v>23523808</v>
       </c>
-      <c r="F257" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="G257" s="6" t="s">
+      <c r="F259" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="258" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="11" t="s">
+      <c r="G259" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="B258" s="11" t="s">
+    </row>
+    <row r="260" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C258" s="11" t="s">
+      <c r="B260" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D258" s="11" t="s">
+      <c r="C260" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="E258" s="25" t="n">
+      <c r="D260" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E260" s="25" t="n">
         <v>18524249</v>
       </c>
-      <c r="F258" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="G258" s="6" t="s">
+      <c r="F260" s="11" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="259" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="11" t="s">
+      <c r="G260" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B259" s="11" t="s">
+    </row>
+    <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C259" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D259" s="11" t="s">
+      <c r="B261" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="E259" s="11" t="n">
+      <c r="C261" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D261" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E261" s="11" t="n">
         <v>25913522</v>
       </c>
-      <c r="F259" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="G259" s="6" t="s">
+      <c r="F261" s="11" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="11" t="s">
+      <c r="G261" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B260" s="11" t="s">
+    </row>
+    <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C260" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D260" s="11" t="s">
+      <c r="B262" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="E260" s="11" t="n">
-        <v>16800737</v>
-      </c>
-      <c r="F260" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="G260" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="11" t="s">
+      <c r="C262" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D262" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="B261" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C261" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D261" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="E261" s="11" t="n">
-        <v>16800737</v>
-      </c>
-      <c r="F261" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G261" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="262" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B262" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C262" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D262" s="11" t="s">
-        <v>177</v>
       </c>
       <c r="E262" s="11" t="n">
         <v>16800737</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G262" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="263" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B263" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C263" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D263" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E263" s="11" t="n">
         <v>16800737</v>
       </c>
       <c r="F263" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G263" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B264" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C264" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D264" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E264" s="11" t="n">
+        <v>16800737</v>
+      </c>
+      <c r="F264" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G264" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="G263" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="32"/>
-      <c r="B264" s="32"/>
-      <c r="C264" s="32"/>
-      <c r="D264" s="32"/>
-      <c r="E264" s="32"/>
-      <c r="F264" s="32"/>
-      <c r="G264" s="32"/>
-    </row>
-    <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="24" t="s">
+      <c r="B265" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C265" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D265" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E265" s="11" t="n">
+        <v>16800737</v>
+      </c>
+      <c r="F265" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="B265" s="24"/>
-      <c r="C265" s="24"/>
-      <c r="D265" s="24"/>
-      <c r="E265" s="24"/>
-      <c r="F265" s="24"/>
-    </row>
-    <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A266" s="33" t="s">
+      <c r="G265" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="32"/>
+      <c r="B266" s="32"/>
+      <c r="C266" s="32"/>
+      <c r="D266" s="32"/>
+      <c r="E266" s="32"/>
+      <c r="F266" s="32"/>
+      <c r="G266" s="32"/>
+    </row>
+    <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B266" s="33"/>
-      <c r="C266" s="33"/>
-      <c r="D266" s="33"/>
-      <c r="E266" s="33"/>
-      <c r="F266" s="33"/>
-    </row>
-    <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="33"/>
-      <c r="B267" s="33"/>
-      <c r="C267" s="33"/>
-      <c r="D267" s="33"/>
-      <c r="E267" s="33"/>
-      <c r="F267" s="33"/>
-    </row>
-    <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="33"/>
+      <c r="B267" s="24"/>
+      <c r="C267" s="24"/>
+      <c r="D267" s="24"/>
+      <c r="E267" s="24"/>
+      <c r="F267" s="24"/>
+    </row>
+    <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A268" s="33" t="s">
+        <v>185</v>
+      </c>
       <c r="B268" s="33"/>
       <c r="C268" s="33"/>
       <c r="D268" s="33"/>
       <c r="E268" s="33"/>
       <c r="F268" s="33"/>
     </row>
-    <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="34"/>
-      <c r="B269" s="34"/>
-      <c r="C269" s="34"/>
-      <c r="D269" s="34"/>
-      <c r="E269" s="34"/>
-      <c r="F269" s="34"/>
+    <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="33"/>
+      <c r="B269" s="33"/>
+      <c r="C269" s="33"/>
+      <c r="D269" s="33"/>
+      <c r="E269" s="33"/>
+      <c r="F269" s="33"/>
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="B270" s="24"/>
-      <c r="C270" s="24"/>
-      <c r="D270" s="24"/>
-      <c r="E270" s="24"/>
-      <c r="F270" s="24"/>
-    </row>
-    <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A271" s="10" t="s">
+      <c r="A270" s="33"/>
+      <c r="B270" s="33"/>
+      <c r="C270" s="33"/>
+      <c r="D270" s="33"/>
+      <c r="E270" s="33"/>
+      <c r="F270" s="33"/>
+    </row>
+    <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="34"/>
+      <c r="B271" s="34"/>
+      <c r="C271" s="34"/>
+      <c r="D271" s="34"/>
+      <c r="E271" s="34"/>
+      <c r="F271" s="34"/>
+    </row>
+    <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B271" s="10"/>
-      <c r="C271" s="10"/>
-      <c r="D271" s="10"/>
-      <c r="E271" s="10"/>
-      <c r="F271" s="10"/>
-    </row>
-    <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="10"/>
-      <c r="B272" s="10"/>
-      <c r="C272" s="10"/>
-      <c r="D272" s="10"/>
-      <c r="E272" s="10"/>
-      <c r="F272" s="10"/>
-    </row>
-    <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="10"/>
+      <c r="B272" s="24"/>
+      <c r="C272" s="24"/>
+      <c r="D272" s="24"/>
+      <c r="E272" s="24"/>
+      <c r="F272" s="24"/>
+    </row>
+    <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A273" s="10" t="s">
+        <v>187</v>
+      </c>
       <c r="B273" s="10"/>
       <c r="C273" s="10"/>
       <c r="D273" s="10"/>
@@ -4169,38 +4179,38 @@
       <c r="F273" s="10"/>
     </row>
     <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="14"/>
-      <c r="B274" s="14"/>
-      <c r="C274" s="14"/>
-      <c r="D274" s="14"/>
-      <c r="E274" s="14"/>
-      <c r="F274" s="14"/>
+      <c r="A274" s="10"/>
+      <c r="B274" s="10"/>
+      <c r="C274" s="10"/>
+      <c r="D274" s="10"/>
+      <c r="E274" s="10"/>
+      <c r="F274" s="10"/>
     </row>
     <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="B275" s="24"/>
-      <c r="C275" s="24"/>
-      <c r="D275" s="24"/>
-      <c r="E275" s="24"/>
-      <c r="F275" s="24"/>
+      <c r="A275" s="10"/>
+      <c r="B275" s="10"/>
+      <c r="C275" s="10"/>
+      <c r="D275" s="10"/>
+      <c r="E275" s="10"/>
+      <c r="F275" s="10"/>
     </row>
     <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="35"/>
-      <c r="B276" s="35"/>
-      <c r="C276" s="35"/>
-      <c r="D276" s="35"/>
-      <c r="E276" s="35"/>
-      <c r="F276" s="35"/>
+      <c r="A276" s="14"/>
+      <c r="B276" s="14"/>
+      <c r="C276" s="14"/>
+      <c r="D276" s="14"/>
+      <c r="E276" s="14"/>
+      <c r="F276" s="14"/>
     </row>
     <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="35"/>
-      <c r="B277" s="35"/>
-      <c r="C277" s="35"/>
-      <c r="D277" s="35"/>
-      <c r="E277" s="35"/>
-      <c r="F277" s="35"/>
+      <c r="A277" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B277" s="24"/>
+      <c r="C277" s="24"/>
+      <c r="D277" s="24"/>
+      <c r="E277" s="24"/>
+      <c r="F277" s="24"/>
     </row>
     <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="35"/>
@@ -4210,7 +4220,7 @@
       <c r="E278" s="35"/>
       <c r="F278" s="35"/>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="35"/>
       <c r="B279" s="35"/>
       <c r="C279" s="35"/>
@@ -4219,66 +4229,66 @@
       <c r="F279" s="35"/>
     </row>
     <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="32"/>
-      <c r="B280" s="32"/>
-      <c r="C280" s="32"/>
-      <c r="D280" s="32"/>
-      <c r="E280" s="32"/>
-      <c r="F280" s="32"/>
-    </row>
-    <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B281" s="4"/>
-      <c r="C281" s="4"/>
-      <c r="D281" s="4"/>
-      <c r="E281" s="4"/>
-      <c r="F281" s="4"/>
-    </row>
-    <row r="282" customFormat="false" ht="98.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A282" s="8" t="s">
+      <c r="A280" s="35"/>
+      <c r="B280" s="35"/>
+      <c r="C280" s="35"/>
+      <c r="D280" s="35"/>
+      <c r="E280" s="35"/>
+      <c r="F280" s="35"/>
+    </row>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A281" s="35"/>
+      <c r="B281" s="35"/>
+      <c r="C281" s="35"/>
+      <c r="D281" s="35"/>
+      <c r="E281" s="35"/>
+      <c r="F281" s="35"/>
+    </row>
+    <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="32"/>
+      <c r="B282" s="32"/>
+      <c r="C282" s="32"/>
+      <c r="D282" s="32"/>
+      <c r="E282" s="32"/>
+      <c r="F282" s="32"/>
+    </row>
+    <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B282" s="8"/>
-      <c r="C282" s="8"/>
-      <c r="D282" s="8"/>
-      <c r="E282" s="8"/>
-      <c r="F282" s="8"/>
-    </row>
-    <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="36"/>
-      <c r="B283" s="36"/>
-      <c r="C283" s="36"/>
-      <c r="D283" s="36"/>
-      <c r="E283" s="36"/>
-      <c r="F283" s="36"/>
-    </row>
-    <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="24" t="s">
+      <c r="B283" s="4"/>
+      <c r="C283" s="4"/>
+      <c r="D283" s="4"/>
+      <c r="E283" s="4"/>
+      <c r="F283" s="4"/>
+    </row>
+    <row r="284" customFormat="false" ht="98.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A284" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B284" s="24"/>
-      <c r="C284" s="24"/>
-      <c r="D284" s="24"/>
-      <c r="E284" s="24"/>
-      <c r="F284" s="24"/>
+      <c r="B284" s="8"/>
+      <c r="C284" s="8"/>
+      <c r="D284" s="8"/>
+      <c r="E284" s="8"/>
+      <c r="F284" s="8"/>
     </row>
     <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="11"/>
-      <c r="B285" s="11"/>
-      <c r="C285" s="11"/>
-      <c r="D285" s="11"/>
-      <c r="E285" s="11"/>
-      <c r="F285" s="11"/>
+      <c r="A285" s="36"/>
+      <c r="B285" s="36"/>
+      <c r="C285" s="36"/>
+      <c r="D285" s="36"/>
+      <c r="E285" s="36"/>
+      <c r="F285" s="36"/>
     </row>
     <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="11"/>
-      <c r="B286" s="11"/>
-      <c r="C286" s="11"/>
-      <c r="D286" s="11"/>
-      <c r="E286" s="11"/>
-      <c r="F286" s="11"/>
+      <c r="A286" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="B286" s="24"/>
+      <c r="C286" s="24"/>
+      <c r="D286" s="24"/>
+      <c r="E286" s="24"/>
+      <c r="F286" s="24"/>
     </row>
     <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="11"/>
@@ -4297,256 +4307,244 @@
       <c r="F288" s="11"/>
     </row>
     <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="37"/>
-      <c r="B289" s="37"/>
-      <c r="C289" s="37"/>
-      <c r="D289" s="37"/>
-      <c r="E289" s="37"/>
-      <c r="F289" s="37"/>
+      <c r="A289" s="11"/>
+      <c r="B289" s="11"/>
+      <c r="C289" s="11"/>
+      <c r="D289" s="11"/>
+      <c r="E289" s="11"/>
+      <c r="F289" s="11"/>
     </row>
     <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B290" s="38"/>
-      <c r="C290" s="38"/>
-      <c r="D290" s="38"/>
-      <c r="E290" s="38"/>
-      <c r="F290" s="38"/>
-    </row>
-    <row r="291" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A291" s="12" t="s">
+      <c r="A290" s="11"/>
+      <c r="B290" s="11"/>
+      <c r="C290" s="11"/>
+      <c r="D290" s="11"/>
+      <c r="E290" s="11"/>
+      <c r="F290" s="11"/>
+    </row>
+    <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="37"/>
+      <c r="B291" s="37"/>
+      <c r="C291" s="37"/>
+      <c r="D291" s="37"/>
+      <c r="E291" s="37"/>
+      <c r="F291" s="37"/>
+    </row>
+    <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B292" s="38"/>
+      <c r="C292" s="38"/>
+      <c r="D292" s="38"/>
+      <c r="E292" s="38"/>
+      <c r="F292" s="38"/>
+    </row>
+    <row r="293" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A293" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B291" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="C291" s="12" t="s">
+      <c r="B293" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="D291" s="12"/>
-      <c r="E291" s="33" t="s">
+      <c r="C293" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="F291" s="33"/>
-    </row>
-    <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B292" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C292" s="24" t="s">
+      <c r="D293" s="12"/>
+      <c r="E293" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="D292" s="24"/>
-      <c r="E292" s="12"/>
-      <c r="F292" s="12"/>
-    </row>
-    <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B293" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="C293" s="24" t="s">
-        <v>197</v>
-      </c>
-      <c r="D293" s="24"/>
-      <c r="E293" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="F293" s="24"/>
+      <c r="F293" s="33"/>
     </row>
     <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B294" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C294" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="D294" s="24"/>
+      <c r="E294" s="12"/>
+      <c r="F294" s="12"/>
+    </row>
+    <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B295" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C295" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="D295" s="24"/>
+      <c r="E295" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="F295" s="24"/>
+    </row>
+    <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B294" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C294" s="24" t="s">
+      <c r="B296" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C296" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="D296" s="24"/>
+      <c r="E296" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="F296" s="24"/>
+    </row>
+    <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C297" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="D297" s="39"/>
+      <c r="E297" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="F297" s="7"/>
+    </row>
+    <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C298" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D298" s="40"/>
+      <c r="E298" s="41"/>
+      <c r="F298" s="41"/>
+    </row>
+    <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C299" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="D299" s="40"/>
+      <c r="E299" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="D294" s="24"/>
-      <c r="E294" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="F294" s="24"/>
-    </row>
-    <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B295" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C295" s="39" t="s">
-        <v>199</v>
-      </c>
-      <c r="D295" s="39"/>
-      <c r="E295" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="F295" s="7"/>
-    </row>
-    <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B296" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C296" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="D296" s="40"/>
-      <c r="E296" s="41"/>
-      <c r="F296" s="41"/>
-    </row>
-    <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B297" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C297" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="D297" s="40"/>
-      <c r="E297" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="F297" s="41"/>
-    </row>
-    <row r="298" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="11"/>
-      <c r="B298" s="6"/>
-      <c r="C298" s="7"/>
-      <c r="D298" s="7"/>
-      <c r="E298" s="7"/>
-      <c r="F298" s="7"/>
-    </row>
-    <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="11"/>
-      <c r="B299" s="6"/>
-      <c r="C299" s="7"/>
-      <c r="D299" s="7"/>
-      <c r="E299" s="7"/>
-      <c r="F299" s="7"/>
+      <c r="F299" s="41"/>
     </row>
     <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="42"/>
-      <c r="B300" s="43"/>
-      <c r="C300" s="43"/>
-      <c r="D300" s="43"/>
-      <c r="E300" s="43"/>
-      <c r="F300" s="43"/>
+      <c r="A300" s="11"/>
+      <c r="B300" s="6"/>
+      <c r="C300" s="7"/>
+      <c r="D300" s="7"/>
+      <c r="E300" s="7"/>
+      <c r="F300" s="7"/>
     </row>
     <row r="301" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="44" t="s">
-        <v>204</v>
-      </c>
-      <c r="B301" s="44"/>
-      <c r="C301" s="44"/>
-      <c r="D301" s="44"/>
-      <c r="E301" s="44"/>
-      <c r="F301" s="44"/>
-      <c r="G301" s="44"/>
-      <c r="H301" s="44"/>
-      <c r="I301" s="44"/>
-      <c r="J301" s="44"/>
+      <c r="A301" s="11"/>
+      <c r="B301" s="6"/>
+      <c r="C301" s="7"/>
+      <c r="D301" s="7"/>
+      <c r="E301" s="7"/>
+      <c r="F301" s="7"/>
     </row>
     <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="44" t="s">
+      <c r="A302" s="42"/>
+      <c r="B302" s="43"/>
+      <c r="C302" s="43"/>
+      <c r="D302" s="43"/>
+      <c r="E302" s="43"/>
+      <c r="F302" s="43"/>
+    </row>
+    <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="B302" s="44"/>
-      <c r="C302" s="44"/>
-      <c r="D302" s="44"/>
-      <c r="E302" s="44"/>
-      <c r="F302" s="44"/>
-      <c r="G302" s="44"/>
-      <c r="H302" s="44"/>
-      <c r="I302" s="44"/>
-      <c r="J302" s="44"/>
-    </row>
-    <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="39" t="s">
+      <c r="B303" s="44"/>
+      <c r="C303" s="44"/>
+      <c r="D303" s="44"/>
+      <c r="E303" s="44"/>
+      <c r="F303" s="44"/>
+      <c r="G303" s="44"/>
+      <c r="H303" s="44"/>
+      <c r="I303" s="44"/>
+      <c r="J303" s="44"/>
+    </row>
+    <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="44" t="s">
         <v>206</v>
       </c>
-      <c r="B303" s="39"/>
-      <c r="C303" s="39"/>
-      <c r="D303" s="39"/>
-      <c r="E303" s="39"/>
-      <c r="F303" s="39"/>
-      <c r="G303" s="39"/>
-      <c r="H303" s="39"/>
-      <c r="I303" s="39"/>
-      <c r="J303" s="39"/>
-    </row>
-    <row r="304" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="6" t="s">
+      <c r="B304" s="44"/>
+      <c r="C304" s="44"/>
+      <c r="D304" s="44"/>
+      <c r="E304" s="44"/>
+      <c r="F304" s="44"/>
+      <c r="G304" s="44"/>
+      <c r="H304" s="44"/>
+      <c r="I304" s="44"/>
+      <c r="J304" s="44"/>
+    </row>
+    <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B305" s="39"/>
+      <c r="C305" s="39"/>
+      <c r="D305" s="39"/>
+      <c r="E305" s="39"/>
+      <c r="F305" s="39"/>
+      <c r="G305" s="39"/>
+      <c r="H305" s="39"/>
+      <c r="I305" s="39"/>
+      <c r="J305" s="39"/>
+    </row>
+    <row r="306" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B304" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C304" s="7"/>
-      <c r="D304" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E304" s="7"/>
-      <c r="F304" s="7" t="s">
+      <c r="B306" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C306" s="7"/>
+      <c r="D306" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="G304" s="6" t="s">
+      <c r="E306" s="7"/>
+      <c r="F306" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="H304" s="45" t="s">
+      <c r="G306" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="I304" s="7" t="s">
+      <c r="H306" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="J304" s="7" t="s">
+      <c r="I306" s="7" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B305" s="7"/>
-      <c r="C305" s="7"/>
-      <c r="D305" s="7"/>
-      <c r="E305" s="7"/>
-      <c r="F305" s="7"/>
-      <c r="G305" s="6"/>
-      <c r="H305" s="6"/>
-      <c r="I305" s="6"/>
-      <c r="J305" s="6"/>
-    </row>
-    <row r="306" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B306" s="7"/>
-      <c r="C306" s="7"/>
-      <c r="D306" s="7"/>
-      <c r="E306" s="7"/>
-      <c r="F306" s="7"/>
-      <c r="G306" s="6"/>
-      <c r="H306" s="6"/>
-      <c r="I306" s="6"/>
-      <c r="J306" s="6"/>
+      <c r="J306" s="7" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="307" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B307" s="7"/>
       <c r="C307" s="7"/>
@@ -4560,7 +4558,7 @@
     </row>
     <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B308" s="7"/>
       <c r="C308" s="7"/>
@@ -4573,89 +4571,89 @@
       <c r="J308" s="6"/>
     </row>
     <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="46"/>
-      <c r="B309" s="46"/>
-      <c r="C309" s="46"/>
-      <c r="D309" s="46"/>
-      <c r="E309" s="46"/>
-      <c r="F309" s="46"/>
-      <c r="G309" s="46"/>
-      <c r="H309" s="46"/>
-      <c r="I309" s="46"/>
+      <c r="A309" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B309" s="7"/>
+      <c r="C309" s="7"/>
+      <c r="D309" s="7"/>
+      <c r="E309" s="7"/>
+      <c r="F309" s="7"/>
+      <c r="G309" s="6"/>
+      <c r="H309" s="6"/>
+      <c r="I309" s="6"/>
+      <c r="J309" s="6"/>
     </row>
     <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="39" t="s">
+      <c r="A310" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B310" s="7"/>
+      <c r="C310" s="7"/>
+      <c r="D310" s="7"/>
+      <c r="E310" s="7"/>
+      <c r="F310" s="7"/>
+      <c r="G310" s="6"/>
+      <c r="H310" s="6"/>
+      <c r="I310" s="6"/>
+      <c r="J310" s="6"/>
+    </row>
+    <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A311" s="46"/>
+      <c r="B311" s="46"/>
+      <c r="C311" s="46"/>
+      <c r="D311" s="46"/>
+      <c r="E311" s="46"/>
+      <c r="F311" s="46"/>
+      <c r="G311" s="46"/>
+      <c r="H311" s="46"/>
+      <c r="I311" s="46"/>
+    </row>
+    <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A312" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="B312" s="39"/>
+      <c r="C312" s="39"/>
+      <c r="D312" s="39"/>
+      <c r="E312" s="39"/>
+      <c r="F312" s="39"/>
+      <c r="G312" s="39"/>
+      <c r="H312" s="39"/>
+      <c r="I312" s="39"/>
+      <c r="J312" s="39"/>
+    </row>
+    <row r="313" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A313" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C313" s="7"/>
+      <c r="D313" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E313" s="7"/>
+      <c r="F313" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="G313" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="H313" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="I313" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="J313" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B310" s="39"/>
-      <c r="C310" s="39"/>
-      <c r="D310" s="39"/>
-      <c r="E310" s="39"/>
-      <c r="F310" s="39"/>
-      <c r="G310" s="39"/>
-      <c r="H310" s="39"/>
-      <c r="I310" s="39"/>
-      <c r="J310" s="39"/>
-    </row>
-    <row r="311" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B311" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C311" s="7"/>
-      <c r="D311" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E311" s="7"/>
-      <c r="F311" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="G311" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="H311" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="I311" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="J311" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B312" s="7"/>
-      <c r="C312" s="7"/>
-      <c r="D312" s="7"/>
-      <c r="E312" s="7"/>
-      <c r="F312" s="7"/>
-      <c r="G312" s="6"/>
-      <c r="H312" s="6"/>
-      <c r="I312" s="6"/>
-      <c r="J312" s="6"/>
-    </row>
-    <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B313" s="7"/>
-      <c r="C313" s="7"/>
-      <c r="D313" s="7"/>
-      <c r="E313" s="7"/>
-      <c r="F313" s="7"/>
-      <c r="G313" s="6"/>
-      <c r="H313" s="6"/>
-      <c r="I313" s="6"/>
-      <c r="J313" s="6"/>
     </row>
     <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B314" s="7"/>
       <c r="C314" s="7"/>
@@ -4669,7 +4667,7 @@
     </row>
     <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B315" s="7"/>
       <c r="C315" s="7"/>
@@ -4682,90 +4680,90 @@
       <c r="J315" s="6"/>
     </row>
     <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="3"/>
-      <c r="B316" s="47"/>
-      <c r="C316" s="47"/>
-      <c r="D316" s="47"/>
-      <c r="E316" s="47"/>
-      <c r="F316" s="47"/>
-      <c r="G316" s="3"/>
-      <c r="H316" s="3"/>
-      <c r="I316" s="3"/>
-      <c r="J316" s="3"/>
+      <c r="A316" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B316" s="7"/>
+      <c r="C316" s="7"/>
+      <c r="D316" s="7"/>
+      <c r="E316" s="7"/>
+      <c r="F316" s="7"/>
+      <c r="G316" s="6"/>
+      <c r="H316" s="6"/>
+      <c r="I316" s="6"/>
+      <c r="J316" s="6"/>
     </row>
     <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="B317" s="39"/>
-      <c r="C317" s="39"/>
-      <c r="D317" s="39"/>
-      <c r="E317" s="39"/>
-      <c r="F317" s="39"/>
-      <c r="G317" s="39"/>
-      <c r="H317" s="39"/>
-      <c r="I317" s="39"/>
-      <c r="J317" s="39"/>
-    </row>
-    <row r="318" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="6" t="s">
+      <c r="A317" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B317" s="7"/>
+      <c r="C317" s="7"/>
+      <c r="D317" s="7"/>
+      <c r="E317" s="7"/>
+      <c r="F317" s="7"/>
+      <c r="G317" s="6"/>
+      <c r="H317" s="6"/>
+      <c r="I317" s="6"/>
+      <c r="J317" s="6"/>
+    </row>
+    <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A318" s="3"/>
+      <c r="B318" s="47"/>
+      <c r="C318" s="47"/>
+      <c r="D318" s="47"/>
+      <c r="E318" s="47"/>
+      <c r="F318" s="47"/>
+      <c r="G318" s="3"/>
+      <c r="H318" s="3"/>
+      <c r="I318" s="3"/>
+      <c r="J318" s="3"/>
+    </row>
+    <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A319" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="B319" s="39"/>
+      <c r="C319" s="39"/>
+      <c r="D319" s="39"/>
+      <c r="E319" s="39"/>
+      <c r="F319" s="39"/>
+      <c r="G319" s="39"/>
+      <c r="H319" s="39"/>
+      <c r="I319" s="39"/>
+      <c r="J319" s="39"/>
+    </row>
+    <row r="320" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A320" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B318" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C318" s="7"/>
-      <c r="D318" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E318" s="7"/>
-      <c r="F318" s="7" t="s">
+      <c r="B320" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C320" s="7"/>
+      <c r="D320" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="G318" s="6" t="s">
+      <c r="E320" s="7"/>
+      <c r="F320" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="H318" s="45" t="s">
+      <c r="G320" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="I318" s="7" t="s">
+      <c r="H320" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="J318" s="7" t="s">
+      <c r="I320" s="7" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B319" s="7"/>
-      <c r="C319" s="7"/>
-      <c r="D319" s="7"/>
-      <c r="E319" s="7"/>
-      <c r="F319" s="7"/>
-      <c r="G319" s="6"/>
-      <c r="H319" s="6"/>
-      <c r="I319" s="6"/>
-      <c r="J319" s="6"/>
-    </row>
-    <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B320" s="7"/>
-      <c r="C320" s="7"/>
-      <c r="D320" s="7"/>
-      <c r="E320" s="7"/>
-      <c r="F320" s="7"/>
-      <c r="G320" s="6"/>
-      <c r="H320" s="6"/>
-      <c r="I320" s="6"/>
-      <c r="J320" s="6"/>
+      <c r="J320" s="7" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B321" s="7"/>
       <c r="C321" s="7"/>
@@ -4779,7 +4777,7 @@
     </row>
     <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B322" s="7"/>
       <c r="C322" s="7"/>
@@ -4792,90 +4790,90 @@
       <c r="J322" s="6"/>
     </row>
     <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="3"/>
-      <c r="B323" s="47"/>
-      <c r="C323" s="47"/>
-      <c r="D323" s="47"/>
-      <c r="E323" s="47"/>
-      <c r="F323" s="47"/>
-      <c r="G323" s="3"/>
-      <c r="H323" s="3"/>
-      <c r="I323" s="3"/>
-      <c r="J323" s="3"/>
+      <c r="A323" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B323" s="7"/>
+      <c r="C323" s="7"/>
+      <c r="D323" s="7"/>
+      <c r="E323" s="7"/>
+      <c r="F323" s="7"/>
+      <c r="G323" s="6"/>
+      <c r="H323" s="6"/>
+      <c r="I323" s="6"/>
+      <c r="J323" s="6"/>
     </row>
     <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="B324" s="39"/>
-      <c r="C324" s="39"/>
-      <c r="D324" s="39"/>
-      <c r="E324" s="39"/>
-      <c r="F324" s="39"/>
-      <c r="G324" s="39"/>
-      <c r="H324" s="39"/>
-      <c r="I324" s="39"/>
-      <c r="J324" s="39"/>
-    </row>
-    <row r="325" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="6" t="s">
+      <c r="A324" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B324" s="7"/>
+      <c r="C324" s="7"/>
+      <c r="D324" s="7"/>
+      <c r="E324" s="7"/>
+      <c r="F324" s="7"/>
+      <c r="G324" s="6"/>
+      <c r="H324" s="6"/>
+      <c r="I324" s="6"/>
+      <c r="J324" s="6"/>
+    </row>
+    <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A325" s="3"/>
+      <c r="B325" s="47"/>
+      <c r="C325" s="47"/>
+      <c r="D325" s="47"/>
+      <c r="E325" s="47"/>
+      <c r="F325" s="47"/>
+      <c r="G325" s="3"/>
+      <c r="H325" s="3"/>
+      <c r="I325" s="3"/>
+      <c r="J325" s="3"/>
+    </row>
+    <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A326" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="B326" s="39"/>
+      <c r="C326" s="39"/>
+      <c r="D326" s="39"/>
+      <c r="E326" s="39"/>
+      <c r="F326" s="39"/>
+      <c r="G326" s="39"/>
+      <c r="H326" s="39"/>
+      <c r="I326" s="39"/>
+      <c r="J326" s="39"/>
+    </row>
+    <row r="327" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A327" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B325" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C325" s="7"/>
-      <c r="D325" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E325" s="7"/>
-      <c r="F325" s="7" t="s">
+      <c r="B327" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C327" s="7"/>
+      <c r="D327" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="G325" s="6" t="s">
+      <c r="E327" s="7"/>
+      <c r="F327" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="H325" s="45" t="s">
+      <c r="G327" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="I325" s="7" t="s">
+      <c r="H327" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="J325" s="7" t="s">
+      <c r="I327" s="7" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B326" s="7"/>
-      <c r="C326" s="7"/>
-      <c r="D326" s="7"/>
-      <c r="E326" s="7"/>
-      <c r="F326" s="7"/>
-      <c r="G326" s="6"/>
-      <c r="H326" s="6"/>
-      <c r="I326" s="6"/>
-      <c r="J326" s="6"/>
-    </row>
-    <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B327" s="7"/>
-      <c r="C327" s="7"/>
-      <c r="D327" s="7"/>
-      <c r="E327" s="7"/>
-      <c r="F327" s="7"/>
-      <c r="G327" s="6"/>
-      <c r="H327" s="6"/>
-      <c r="I327" s="6"/>
-      <c r="J327" s="6"/>
+      <c r="J327" s="7" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B328" s="7"/>
       <c r="C328" s="7"/>
@@ -4889,7 +4887,7 @@
     </row>
     <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B329" s="7"/>
       <c r="C329" s="7"/>
@@ -4902,116 +4900,116 @@
       <c r="J329" s="6"/>
     </row>
     <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="3"/>
-      <c r="B330" s="47"/>
-      <c r="C330" s="47"/>
-      <c r="D330" s="47"/>
-      <c r="E330" s="47"/>
-      <c r="F330" s="47"/>
-      <c r="G330" s="3"/>
-      <c r="H330" s="3"/>
-      <c r="I330" s="3"/>
-      <c r="J330" s="3"/>
+      <c r="A330" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B330" s="7"/>
+      <c r="C330" s="7"/>
+      <c r="D330" s="7"/>
+      <c r="E330" s="7"/>
+      <c r="F330" s="7"/>
+      <c r="G330" s="6"/>
+      <c r="H330" s="6"/>
+      <c r="I330" s="6"/>
+      <c r="J330" s="6"/>
     </row>
     <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="48" t="s">
-        <v>216</v>
-      </c>
-      <c r="B331" s="48"/>
-      <c r="C331" s="48"/>
-      <c r="D331" s="48"/>
-      <c r="E331" s="48"/>
-      <c r="F331" s="48"/>
-      <c r="G331" s="48"/>
-      <c r="H331" s="48"/>
-      <c r="I331" s="48"/>
-      <c r="J331" s="48"/>
-    </row>
-    <row r="332" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="6" t="s">
+      <c r="A331" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B331" s="7"/>
+      <c r="C331" s="7"/>
+      <c r="D331" s="7"/>
+      <c r="E331" s="7"/>
+      <c r="F331" s="7"/>
+      <c r="G331" s="6"/>
+      <c r="H331" s="6"/>
+      <c r="I331" s="6"/>
+      <c r="J331" s="6"/>
+    </row>
+    <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A332" s="3"/>
+      <c r="B332" s="47"/>
+      <c r="C332" s="47"/>
+      <c r="D332" s="47"/>
+      <c r="E332" s="47"/>
+      <c r="F332" s="47"/>
+      <c r="G332" s="3"/>
+      <c r="H332" s="3"/>
+      <c r="I332" s="3"/>
+      <c r="J332" s="3"/>
+    </row>
+    <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A333" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="B333" s="48"/>
+      <c r="C333" s="48"/>
+      <c r="D333" s="48"/>
+      <c r="E333" s="48"/>
+      <c r="F333" s="48"/>
+      <c r="G333" s="48"/>
+      <c r="H333" s="48"/>
+      <c r="I333" s="48"/>
+      <c r="J333" s="48"/>
+    </row>
+    <row r="334" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A334" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B332" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C332" s="7"/>
-      <c r="D332" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E332" s="7"/>
-      <c r="F332" s="7" t="s">
+      <c r="B334" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C334" s="7"/>
+      <c r="D334" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="G332" s="6" t="s">
+      <c r="E334" s="7"/>
+      <c r="F334" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="H332" s="45" t="s">
+      <c r="G334" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="I332" s="7" t="s">
+      <c r="H334" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="J332" s="7" t="s">
+      <c r="I334" s="7" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B333" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C333" s="7"/>
-      <c r="D333" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="E333" s="7"/>
-      <c r="F333" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="G333" s="49" t="n">
-        <v>45901</v>
-      </c>
-      <c r="H333" s="6"/>
-      <c r="I333" s="50" t="n">
-        <v>23351725</v>
-      </c>
-      <c r="J333" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B334" s="7"/>
-      <c r="C334" s="7"/>
-      <c r="D334" s="7"/>
-      <c r="E334" s="7"/>
-      <c r="F334" s="7"/>
-      <c r="G334" s="6"/>
-      <c r="H334" s="6"/>
-      <c r="I334" s="6"/>
-      <c r="J334" s="6"/>
+      <c r="J334" s="7" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B335" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>218</v>
+      </c>
       <c r="C335" s="7"/>
-      <c r="D335" s="7"/>
+      <c r="D335" s="7" t="s">
+        <v>219</v>
+      </c>
       <c r="E335" s="7"/>
-      <c r="F335" s="7"/>
-      <c r="G335" s="6"/>
+      <c r="F335" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="G335" s="49" t="n">
+        <v>45901</v>
+      </c>
       <c r="H335" s="6"/>
-      <c r="I335" s="6"/>
-      <c r="J335" s="6"/>
+      <c r="I335" s="50" t="n">
+        <v>23351725</v>
+      </c>
+      <c r="J335" s="6" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B336" s="7"/>
       <c r="C336" s="7"/>
@@ -5024,239 +5022,235 @@
       <c r="J336" s="6"/>
     </row>
     <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="3"/>
-      <c r="B337" s="47"/>
-      <c r="C337" s="47"/>
-      <c r="D337" s="47"/>
-      <c r="E337" s="47"/>
-      <c r="F337" s="47"/>
-      <c r="G337" s="3"/>
-      <c r="H337" s="3"/>
-      <c r="I337" s="3"/>
-      <c r="J337" s="3"/>
+      <c r="A337" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B337" s="7"/>
+      <c r="C337" s="7"/>
+      <c r="D337" s="7"/>
+      <c r="E337" s="7"/>
+      <c r="F337" s="7"/>
+      <c r="G337" s="6"/>
+      <c r="H337" s="6"/>
+      <c r="I337" s="6"/>
+      <c r="J337" s="6"/>
+    </row>
+    <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A338" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B338" s="7"/>
+      <c r="C338" s="7"/>
+      <c r="D338" s="7"/>
+      <c r="E338" s="7"/>
+      <c r="F338" s="7"/>
+      <c r="G338" s="6"/>
+      <c r="H338" s="6"/>
+      <c r="I338" s="6"/>
+      <c r="J338" s="6"/>
     </row>
     <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="44" t="s">
-        <v>221</v>
-      </c>
-      <c r="B339" s="44"/>
-      <c r="C339" s="44"/>
-      <c r="D339" s="44"/>
-      <c r="E339" s="44"/>
-      <c r="F339" s="44"/>
-    </row>
-    <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="44" t="s">
+      <c r="A339" s="3"/>
+      <c r="B339" s="47"/>
+      <c r="C339" s="47"/>
+      <c r="D339" s="47"/>
+      <c r="E339" s="47"/>
+      <c r="F339" s="47"/>
+      <c r="G339" s="3"/>
+      <c r="H339" s="3"/>
+      <c r="I339" s="3"/>
+      <c r="J339" s="3"/>
+    </row>
+    <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A341" s="44" t="s">
         <v>222</v>
       </c>
-      <c r="B340" s="44"/>
-      <c r="C340" s="44"/>
-      <c r="D340" s="44"/>
-      <c r="E340" s="44"/>
-      <c r="F340" s="44"/>
-    </row>
-    <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="51"/>
-      <c r="B341" s="51" t="s">
+      <c r="B341" s="44"/>
+      <c r="C341" s="44"/>
+      <c r="D341" s="44"/>
+      <c r="E341" s="44"/>
+      <c r="F341" s="44"/>
+    </row>
+    <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A342" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C341" s="51"/>
-      <c r="D341" s="51"/>
-      <c r="E341" s="51"/>
-      <c r="F341" s="51"/>
-    </row>
-    <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A342" s="51"/>
-      <c r="B342" s="7" t="s">
+      <c r="B342" s="44"/>
+      <c r="C342" s="44"/>
+      <c r="D342" s="44"/>
+      <c r="E342" s="44"/>
+      <c r="F342" s="44"/>
+    </row>
+    <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="51"/>
+      <c r="B343" s="51" t="s">
         <v>224</v>
       </c>
-      <c r="C342" s="7" t="s">
+      <c r="C343" s="51"/>
+      <c r="D343" s="51"/>
+      <c r="E343" s="51"/>
+      <c r="F343" s="51"/>
+    </row>
+    <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A344" s="51"/>
+      <c r="B344" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D342" s="7"/>
-      <c r="E342" s="45" t="s">
+      <c r="C344" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="F342" s="45"/>
-    </row>
-    <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="6" t="s">
+      <c r="D344" s="7"/>
+      <c r="E344" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="F344" s="45"/>
+    </row>
+    <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A345" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B343" s="6"/>
-      <c r="C343" s="6"/>
-      <c r="D343" s="6"/>
-      <c r="E343" s="6"/>
-      <c r="F343" s="6"/>
-    </row>
-    <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B344" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C344" s="52" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D344" s="52"/>
-      <c r="E344" s="52" t="n">
-        <v>337733.95</v>
-      </c>
-      <c r="F344" s="52"/>
-    </row>
-    <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B345" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="C345" s="52" t="n">
-        <v>756000</v>
-      </c>
-      <c r="D345" s="52"/>
-      <c r="E345" s="52" t="n">
-        <v>440000</v>
-      </c>
-      <c r="F345" s="52"/>
+      <c r="B345" s="6"/>
+      <c r="C345" s="6"/>
+      <c r="D345" s="6"/>
+      <c r="E345" s="6"/>
+      <c r="F345" s="6"/>
     </row>
     <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C346" s="52" t="n">
-        <v>882000</v>
+        <v>450000</v>
       </c>
       <c r="D346" s="52"/>
       <c r="E346" s="52" t="n">
-        <v>268724.76</v>
+        <v>337733.95</v>
       </c>
       <c r="F346" s="52"/>
     </row>
     <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B347" s="39" t="s">
-        <v>230</v>
+        <v>2</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="C347" s="52" t="n">
         <v>756000</v>
       </c>
       <c r="D347" s="52"/>
       <c r="E347" s="52" t="n">
+        <v>440000</v>
+      </c>
+      <c r="F347" s="52"/>
+    </row>
+    <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A348" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B348" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C348" s="52" t="n">
+        <v>882000</v>
+      </c>
+      <c r="D348" s="52"/>
+      <c r="E348" s="52" t="n">
+        <v>268724.76</v>
+      </c>
+      <c r="F348" s="52"/>
+    </row>
+    <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A349" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B349" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="C349" s="52" t="n">
+        <v>756000</v>
+      </c>
+      <c r="D349" s="52"/>
+      <c r="E349" s="52" t="n">
         <v>658414.95</v>
       </c>
-      <c r="F347" s="52"/>
-    </row>
-    <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B348" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="C348" s="53" t="n">
+      <c r="F349" s="52"/>
+    </row>
+    <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A350" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B350" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="C350" s="53" t="n">
         <v>756000</v>
       </c>
-      <c r="D348" s="53"/>
-      <c r="E348" s="53" t="n">
+      <c r="D350" s="53"/>
+      <c r="E350" s="53" t="n">
         <v>306606.14</v>
       </c>
-      <c r="F348" s="53"/>
-    </row>
-    <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="3"/>
-      <c r="B349" s="3"/>
-      <c r="C349" s="3"/>
-      <c r="D349" s="3"/>
-      <c r="E349" s="3"/>
-      <c r="F349" s="3"/>
-    </row>
-    <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="6"/>
-      <c r="B350" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C350" s="7"/>
-      <c r="D350" s="7"/>
-      <c r="E350" s="7"/>
-      <c r="F350" s="7"/>
-    </row>
-    <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A351" s="6" t="s">
+      <c r="F350" s="53"/>
+    </row>
+    <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A351" s="3"/>
+      <c r="B351" s="3"/>
+      <c r="C351" s="3"/>
+      <c r="D351" s="3"/>
+      <c r="E351" s="3"/>
+      <c r="F351" s="3"/>
+    </row>
+    <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A352" s="6"/>
+      <c r="B352" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C352" s="7"/>
+      <c r="D352" s="7"/>
+      <c r="E352" s="7"/>
+      <c r="F352" s="7"/>
+    </row>
+    <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A353" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B351" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C351" s="7" t="s">
+      <c r="B353" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D351" s="7"/>
-      <c r="E351" s="45" t="s">
+      <c r="C353" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="F351" s="45"/>
-    </row>
-    <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B352" s="6" t="s">
+      <c r="D353" s="7"/>
+      <c r="E353" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="C352" s="54" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="D352" s="54"/>
-      <c r="E352" s="54" t="n">
-        <v>1116000</v>
-      </c>
-      <c r="F352" s="54"/>
-    </row>
-    <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B353" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="C353" s="54" t="n">
-        <v>324000</v>
-      </c>
-      <c r="D353" s="54"/>
-      <c r="E353" s="54" t="n">
-        <v>324000</v>
-      </c>
-      <c r="F353" s="54"/>
+      <c r="F353" s="45"/>
     </row>
     <row r="354" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B354" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C354" s="54" t="n">
-        <v>378000</v>
+        <v>1350000</v>
       </c>
       <c r="D354" s="54"/>
       <c r="E354" s="54" t="n">
-        <v>378000</v>
+        <v>1116000</v>
       </c>
       <c r="F354" s="54"/>
     </row>
     <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B355" s="39" t="s">
-        <v>230</v>
+        <v>2</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="C355" s="54" t="n">
         <v>324000</v>
@@ -5268,58 +5262,74 @@
       <c r="F355" s="54"/>
     </row>
     <row r="356" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B356" s="39" t="s">
+      <c r="A356" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B356" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C356" s="54" t="n">
+        <v>378000</v>
+      </c>
+      <c r="D356" s="54"/>
+      <c r="E356" s="54" t="n">
+        <v>378000</v>
+      </c>
+      <c r="F356" s="54"/>
+    </row>
+    <row r="357" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A357" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B357" s="39" t="s">
         <v>231</v>
       </c>
-      <c r="C356" s="55" t="n">
+      <c r="C357" s="54" t="n">
         <v>324000</v>
       </c>
-      <c r="D356" s="55"/>
-      <c r="E356" s="55" t="n">
+      <c r="D357" s="54"/>
+      <c r="E357" s="54" t="n">
+        <v>324000</v>
+      </c>
+      <c r="F357" s="54"/>
+    </row>
+    <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A358" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B358" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="C358" s="55" t="n">
+        <v>324000</v>
+      </c>
+      <c r="D358" s="55"/>
+      <c r="E358" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="F356" s="55"/>
-    </row>
-    <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="44" t="s">
-        <v>233</v>
-      </c>
-      <c r="B358" s="44"/>
-      <c r="C358" s="44"/>
-      <c r="D358" s="44"/>
-      <c r="E358" s="44"/>
-      <c r="F358" s="44"/>
-    </row>
-    <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A359" s="56" t="s">
+      <c r="F358" s="55"/>
+    </row>
+    <row r="360" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="B359" s="56"/>
-      <c r="C359" s="56"/>
-      <c r="D359" s="56"/>
-      <c r="E359" s="56"/>
-      <c r="F359" s="56"/>
-    </row>
-    <row r="360" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="56"/>
-      <c r="B360" s="56"/>
-      <c r="C360" s="56"/>
-      <c r="D360" s="56"/>
-      <c r="E360" s="56"/>
-      <c r="F360" s="56"/>
-    </row>
-    <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="56"/>
+      <c r="B360" s="44"/>
+      <c r="C360" s="44"/>
+      <c r="D360" s="44"/>
+      <c r="E360" s="44"/>
+      <c r="F360" s="44"/>
+    </row>
+    <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A361" s="56" t="s">
+        <v>235</v>
+      </c>
       <c r="B361" s="56"/>
       <c r="C361" s="56"/>
       <c r="D361" s="56"/>
       <c r="E361" s="56"/>
       <c r="F361" s="56"/>
     </row>
-    <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="56"/>
       <c r="B362" s="56"/>
       <c r="C362" s="56"/>
@@ -5327,7 +5337,7 @@
       <c r="E362" s="56"/>
       <c r="F362" s="56"/>
     </row>
-    <row r="363" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="56"/>
       <c r="B363" s="56"/>
       <c r="C363" s="56"/>
@@ -5335,8 +5345,22 @@
       <c r="E363" s="56"/>
       <c r="F363" s="56"/>
     </row>
-    <row r="364" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="365" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="56"/>
+      <c r="B364" s="56"/>
+      <c r="C364" s="56"/>
+      <c r="D364" s="56"/>
+      <c r="E364" s="56"/>
+      <c r="F364" s="56"/>
+    </row>
+    <row r="365" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A365" s="56"/>
+      <c r="B365" s="56"/>
+      <c r="C365" s="56"/>
+      <c r="D365" s="56"/>
+      <c r="E365" s="56"/>
+      <c r="F365" s="56"/>
+    </row>
     <row r="366" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="367" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="368" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -5356,6 +5380,8 @@
     <row r="382" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="383" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="384" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="236">
     <mergeCell ref="A1:F1"/>
@@ -5384,115 +5410,111 @@
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="D46:F46"/>
     <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="D53:F53"/>
     <mergeCell ref="D54:F54"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A93:F93"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A95:F95"/>
     <mergeCell ref="E96:F96"/>
     <mergeCell ref="E97:F97"/>
     <mergeCell ref="E98:F98"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A107:F107"/>
-    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A109:F109"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A111:F111"/>
     <mergeCell ref="A112:F112"/>
-    <mergeCell ref="A113:F114"/>
-    <mergeCell ref="A115:F115"/>
-    <mergeCell ref="A116:F121"/>
-    <mergeCell ref="A122:F122"/>
-    <mergeCell ref="A123:F127"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A129:F132"/>
-    <mergeCell ref="A133:F133"/>
-    <mergeCell ref="A134:F135"/>
-    <mergeCell ref="A137:F137"/>
-    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="A115:F116"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A118:F123"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A125:F129"/>
+    <mergeCell ref="A130:F130"/>
+    <mergeCell ref="A131:F134"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A136:F137"/>
     <mergeCell ref="A139:F139"/>
-    <mergeCell ref="A140:F141"/>
-    <mergeCell ref="A142:F142"/>
-    <mergeCell ref="A143:F148"/>
-    <mergeCell ref="A149:F149"/>
-    <mergeCell ref="A150:F154"/>
-    <mergeCell ref="A155:F155"/>
-    <mergeCell ref="A156:F159"/>
-    <mergeCell ref="A160:F160"/>
-    <mergeCell ref="A161:F162"/>
-    <mergeCell ref="A164:F164"/>
-    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A142:F143"/>
+    <mergeCell ref="A144:F144"/>
+    <mergeCell ref="A145:F150"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A152:F156"/>
+    <mergeCell ref="A157:F157"/>
+    <mergeCell ref="A158:F161"/>
+    <mergeCell ref="A162:F162"/>
+    <mergeCell ref="A163:F164"/>
     <mergeCell ref="A166:F166"/>
-    <mergeCell ref="A167:F168"/>
-    <mergeCell ref="A169:F169"/>
-    <mergeCell ref="A170:F175"/>
-    <mergeCell ref="A176:F176"/>
-    <mergeCell ref="A177:F181"/>
-    <mergeCell ref="A182:F182"/>
-    <mergeCell ref="A183:F186"/>
-    <mergeCell ref="A187:F187"/>
-    <mergeCell ref="A188:F189"/>
-    <mergeCell ref="A191:F191"/>
-    <mergeCell ref="A192:F192"/>
+    <mergeCell ref="A167:F167"/>
+    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A169:F170"/>
+    <mergeCell ref="A171:F171"/>
+    <mergeCell ref="A172:F177"/>
+    <mergeCell ref="A178:F178"/>
+    <mergeCell ref="A179:F183"/>
+    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="A185:F188"/>
+    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="A190:F191"/>
     <mergeCell ref="A193:F193"/>
-    <mergeCell ref="A194:F195"/>
-    <mergeCell ref="A196:F196"/>
-    <mergeCell ref="A197:F202"/>
-    <mergeCell ref="A203:F203"/>
-    <mergeCell ref="A204:F208"/>
-    <mergeCell ref="A209:F209"/>
-    <mergeCell ref="A210:F213"/>
-    <mergeCell ref="A214:F214"/>
-    <mergeCell ref="A215:F216"/>
-    <mergeCell ref="A221:F221"/>
-    <mergeCell ref="A222:F224"/>
-    <mergeCell ref="A225:F225"/>
-    <mergeCell ref="A226:F228"/>
-    <mergeCell ref="A229:F229"/>
-    <mergeCell ref="A230:F233"/>
-    <mergeCell ref="A234:G234"/>
-    <mergeCell ref="A235:G235"/>
+    <mergeCell ref="A194:F194"/>
+    <mergeCell ref="A195:F195"/>
+    <mergeCell ref="A196:F197"/>
+    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A199:F204"/>
+    <mergeCell ref="A205:F205"/>
+    <mergeCell ref="A206:F210"/>
+    <mergeCell ref="A211:F211"/>
+    <mergeCell ref="A212:F215"/>
+    <mergeCell ref="A216:F216"/>
+    <mergeCell ref="A217:F218"/>
+    <mergeCell ref="A223:F223"/>
+    <mergeCell ref="A224:F226"/>
+    <mergeCell ref="A227:F227"/>
+    <mergeCell ref="A228:F230"/>
+    <mergeCell ref="A231:F231"/>
+    <mergeCell ref="A232:F235"/>
     <mergeCell ref="A236:G236"/>
-    <mergeCell ref="A242:G242"/>
-    <mergeCell ref="A243:G243"/>
-    <mergeCell ref="A249:G249"/>
-    <mergeCell ref="A250:G250"/>
+    <mergeCell ref="A237:G237"/>
+    <mergeCell ref="A238:G238"/>
+    <mergeCell ref="A244:G244"/>
+    <mergeCell ref="A245:G245"/>
     <mergeCell ref="A251:G251"/>
-    <mergeCell ref="A264:G264"/>
-    <mergeCell ref="A265:F265"/>
-    <mergeCell ref="A266:F268"/>
-    <mergeCell ref="A269:F269"/>
-    <mergeCell ref="A270:F270"/>
-    <mergeCell ref="A271:F273"/>
-    <mergeCell ref="A274:F274"/>
-    <mergeCell ref="A275:F275"/>
-    <mergeCell ref="A276:F279"/>
-    <mergeCell ref="A280:F280"/>
-    <mergeCell ref="A281:F281"/>
+    <mergeCell ref="A252:G252"/>
+    <mergeCell ref="A253:G253"/>
+    <mergeCell ref="A266:G266"/>
+    <mergeCell ref="A267:F267"/>
+    <mergeCell ref="A268:F270"/>
+    <mergeCell ref="A271:F271"/>
+    <mergeCell ref="A272:F272"/>
+    <mergeCell ref="A273:F275"/>
+    <mergeCell ref="A276:F276"/>
+    <mergeCell ref="A277:F277"/>
+    <mergeCell ref="A278:F281"/>
     <mergeCell ref="A282:F282"/>
+    <mergeCell ref="A283:F283"/>
     <mergeCell ref="A284:F284"/>
-    <mergeCell ref="A285:F288"/>
-    <mergeCell ref="A289:F289"/>
-    <mergeCell ref="C291:D291"/>
-    <mergeCell ref="E291:F291"/>
-    <mergeCell ref="C292:D292"/>
-    <mergeCell ref="E292:F292"/>
+    <mergeCell ref="A286:F286"/>
+    <mergeCell ref="A287:F290"/>
+    <mergeCell ref="A291:F291"/>
     <mergeCell ref="C293:D293"/>
     <mergeCell ref="E293:F293"/>
     <mergeCell ref="C294:D294"/>
@@ -5503,71 +5525,71 @@
     <mergeCell ref="E296:F296"/>
     <mergeCell ref="C297:D297"/>
     <mergeCell ref="E297:F297"/>
-    <mergeCell ref="A301:J301"/>
-    <mergeCell ref="A302:J302"/>
+    <mergeCell ref="C298:D298"/>
+    <mergeCell ref="E298:F298"/>
+    <mergeCell ref="C299:D299"/>
+    <mergeCell ref="E299:F299"/>
     <mergeCell ref="A303:J303"/>
-    <mergeCell ref="B304:C304"/>
-    <mergeCell ref="D304:E304"/>
-    <mergeCell ref="B305:C305"/>
-    <mergeCell ref="D305:E305"/>
+    <mergeCell ref="A304:J304"/>
+    <mergeCell ref="A305:J305"/>
     <mergeCell ref="B306:C306"/>
     <mergeCell ref="D306:E306"/>
     <mergeCell ref="B307:C307"/>
     <mergeCell ref="D307:E307"/>
     <mergeCell ref="B308:C308"/>
     <mergeCell ref="D308:E308"/>
-    <mergeCell ref="A309:I309"/>
-    <mergeCell ref="A310:J310"/>
-    <mergeCell ref="B311:C311"/>
-    <mergeCell ref="D311:E311"/>
-    <mergeCell ref="B312:C312"/>
-    <mergeCell ref="D312:E312"/>
+    <mergeCell ref="B309:C309"/>
+    <mergeCell ref="D309:E309"/>
+    <mergeCell ref="B310:C310"/>
+    <mergeCell ref="D310:E310"/>
+    <mergeCell ref="A311:I311"/>
+    <mergeCell ref="A312:J312"/>
     <mergeCell ref="B313:C313"/>
     <mergeCell ref="D313:E313"/>
     <mergeCell ref="B314:C314"/>
     <mergeCell ref="D314:E314"/>
     <mergeCell ref="B315:C315"/>
     <mergeCell ref="D315:E315"/>
-    <mergeCell ref="A317:J317"/>
-    <mergeCell ref="B318:C318"/>
-    <mergeCell ref="D318:E318"/>
-    <mergeCell ref="B319:C319"/>
-    <mergeCell ref="D319:E319"/>
+    <mergeCell ref="B316:C316"/>
+    <mergeCell ref="D316:E316"/>
+    <mergeCell ref="B317:C317"/>
+    <mergeCell ref="D317:E317"/>
+    <mergeCell ref="A319:J319"/>
     <mergeCell ref="B320:C320"/>
     <mergeCell ref="D320:E320"/>
     <mergeCell ref="B321:C321"/>
     <mergeCell ref="D321:E321"/>
     <mergeCell ref="B322:C322"/>
     <mergeCell ref="D322:E322"/>
-    <mergeCell ref="A324:J324"/>
-    <mergeCell ref="B325:C325"/>
-    <mergeCell ref="D325:E325"/>
-    <mergeCell ref="B326:C326"/>
-    <mergeCell ref="D326:E326"/>
+    <mergeCell ref="B323:C323"/>
+    <mergeCell ref="D323:E323"/>
+    <mergeCell ref="B324:C324"/>
+    <mergeCell ref="D324:E324"/>
+    <mergeCell ref="A326:J326"/>
     <mergeCell ref="B327:C327"/>
     <mergeCell ref="D327:E327"/>
     <mergeCell ref="B328:C328"/>
     <mergeCell ref="D328:E328"/>
     <mergeCell ref="B329:C329"/>
     <mergeCell ref="D329:E329"/>
-    <mergeCell ref="A331:J331"/>
-    <mergeCell ref="B332:C332"/>
-    <mergeCell ref="D332:E332"/>
-    <mergeCell ref="B333:C333"/>
-    <mergeCell ref="D333:E333"/>
+    <mergeCell ref="B330:C330"/>
+    <mergeCell ref="D330:E330"/>
+    <mergeCell ref="B331:C331"/>
+    <mergeCell ref="D331:E331"/>
+    <mergeCell ref="A333:J333"/>
     <mergeCell ref="B334:C334"/>
     <mergeCell ref="D334:E334"/>
     <mergeCell ref="B335:C335"/>
     <mergeCell ref="D335:E335"/>
     <mergeCell ref="B336:C336"/>
     <mergeCell ref="D336:E336"/>
-    <mergeCell ref="A339:F339"/>
-    <mergeCell ref="A340:F340"/>
-    <mergeCell ref="B341:F341"/>
-    <mergeCell ref="C342:D342"/>
-    <mergeCell ref="E342:F342"/>
-    <mergeCell ref="C343:D343"/>
-    <mergeCell ref="E343:F343"/>
+    <mergeCell ref="B337:C337"/>
+    <mergeCell ref="D337:E337"/>
+    <mergeCell ref="B338:C338"/>
+    <mergeCell ref="D338:E338"/>
+    <mergeCell ref="A341:F341"/>
+    <mergeCell ref="A342:F342"/>
+    <mergeCell ref="B343:F343"/>
     <mergeCell ref="C344:D344"/>
     <mergeCell ref="E344:F344"/>
     <mergeCell ref="C345:D345"/>
@@ -5578,12 +5600,12 @@
     <mergeCell ref="E347:F347"/>
     <mergeCell ref="C348:D348"/>
     <mergeCell ref="E348:F348"/>
-    <mergeCell ref="A349:F349"/>
-    <mergeCell ref="B350:F350"/>
-    <mergeCell ref="C351:D351"/>
-    <mergeCell ref="E351:F351"/>
-    <mergeCell ref="C352:D352"/>
-    <mergeCell ref="E352:F352"/>
+    <mergeCell ref="C349:D349"/>
+    <mergeCell ref="E349:F349"/>
+    <mergeCell ref="C350:D350"/>
+    <mergeCell ref="E350:F350"/>
+    <mergeCell ref="A351:F351"/>
+    <mergeCell ref="B352:F352"/>
     <mergeCell ref="C353:D353"/>
     <mergeCell ref="E353:F353"/>
     <mergeCell ref="C354:D354"/>
@@ -5592,12 +5614,16 @@
     <mergeCell ref="E355:F355"/>
     <mergeCell ref="C356:D356"/>
     <mergeCell ref="E356:F356"/>
-    <mergeCell ref="A358:F358"/>
-    <mergeCell ref="A359:F363"/>
+    <mergeCell ref="C357:D357"/>
+    <mergeCell ref="E357:F357"/>
+    <mergeCell ref="C358:D358"/>
+    <mergeCell ref="E358:F358"/>
+    <mergeCell ref="A360:F360"/>
+    <mergeCell ref="A361:F365"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A9" r:id="rId1" display="1.5.- Dirección de Email: manuel.carlevaro@gmail.com"/>
-    <hyperlink ref="A266" r:id="rId2" display="https://libropython.science/"/>
+    <hyperlink ref="A268" r:id="rId2" display="F. Batista y Manuel Carlevaro. Python para Ciencia y Tecnología, 2025. Autoeditado, ISBN: 978-631- 00-9794-7. https://libropython.science/."/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.315277777777778" right="0.315277777777778" top="0.354166666666667" bottom="0.354166666666667" header="0.511811023622047" footer="0.511811023622047"/>
